--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -751,7 +751,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1079,10 +1079,8 @@
           <t>Manoj Subedi</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9860395278</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9860395278</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1097,10 +1095,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9860395278</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9860395278</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -1117,10 +1113,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.72776</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.72776</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -1176,25 +1170,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L12-2</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.35325</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.35325</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv not working   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -612,7 +612,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>IPTV Issue</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -628,7 +628,53 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -643,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -671,7 +717,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -682,16 +728,42 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
+      <c r="B5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -718,12 +790,12 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -733,7 +805,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
@@ -751,12 +823,12 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
     <col width="16" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
@@ -1218,6 +1290,430 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 8:30 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344523</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Rudra bhattarai</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Rudra bhattarai</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9851069446</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 08:30:15 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9851069446</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:43:41 AM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 08:30:15 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>27.737687</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Gurung tole, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>20:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>L28-7</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>85.367328</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 46m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 8:17 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Set up box issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Set up box issue</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344915</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Chandra Bahadur Thapa</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Chandra Bahadur Thapa</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9803803944</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 08:17:40 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9803803944</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 02:44:24 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 08:17:40 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.733464</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Helambu Driving School - Drivers license training school P9M6+9FH, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>15:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L48-6</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.361761</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Set up box issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 33m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Set up box issue   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -823,7 +823,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1357,10 +1357,8 @@
           <t>Rudra bhattarai</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9851069446</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9851069446</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1375,10 +1373,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9851069446</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9851069446</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1395,10 +1391,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.737687</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.737687</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1450,25 +1444,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>L28-7</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.367328</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.367328</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1569,10 +1559,8 @@
           <t>Chandra Bahadur Thapa</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9803803944</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9803803944</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1587,10 +1575,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9803803944</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9803803944</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1607,10 +1593,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.733464</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.733464</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1662,25 +1646,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>L48-6</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.361761</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.361761</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : Set up box issue   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,36 +528,54 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -628,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -651,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -662,19 +680,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -689,12 +707,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,10 +724,15 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -717,39 +741,48 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="D3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="D4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -760,10 +793,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>3</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -777,12 +813,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -791,7 +827,7 @@
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -807,29 +843,29 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="31" customWidth="1" min="32" max="32"/>
     <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="17" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="45" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="16" customWidth="1" min="50" max="50"/>
+    <col width="20" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1691,6 +1727,218 @@
       <c r="AX4" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 9:06 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344520</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Nabindra Chaulagain</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Nabindra Chaulagain</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9841295418</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 09:06:23 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9841295418</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:42:16 AM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 09:06:23 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.69502</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Near Baneshwor Recreation Center,Baneshowr,Kathmandu	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>Nabindrachaulagain@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L50-4</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.33543</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 24m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Assigned / Transferred to MS / Other Handler</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -787,19 +787,35 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Other / Uncategorized</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4" t="n">
+      <c r="C6" s="4" t="n">
         <v>4</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -813,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -859,7 +875,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -1797,10 +1813,8 @@
           <t>Nabindra Chaulagain</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9841295418</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9841295418</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1815,10 +1829,8 @@
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>9841295418</t>
-        </is>
+      <c r="U5" s="3" t="n">
+        <v>9841295418</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1835,10 +1847,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.69502</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.69502</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1890,47 +1900,43 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L50-4</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.33543</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.33543</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 24m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Assigned / Transferred to MS / Other Handler</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 24m</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
-        <is>
-          <t>Assigned / Transferred to MS / Other Handler</t>
-        </is>
-      </c>
-      <c r="AV5" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -1939,6 +1945,114 @@
       <c r="AX5" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 9:30 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr"/>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -748,10 +748,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -812,10 +812,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -829,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -875,7 +875,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -2056,6 +2056,218 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 9:34 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344570</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Ruplal Gyawali</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Ruplal Gyawali</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9868264272</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:11:55 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9868264272</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:11:55 AM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 09:34:09 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.670915</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>near by Dream Garden Resort - Family restaurant Budhanilkantha 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>gyawaliruplal80@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L42-3</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.44147</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 22m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 22m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -829,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AX9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2123,10 +2123,8 @@
           <t>Ruplal Gyawali</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9868264272</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9868264272</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2141,10 +2139,8 @@
       </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>9868264272</t>
-        </is>
+      <c r="U7" s="3" t="n">
+        <v>9868264272</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -2161,10 +2157,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.670915</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.670915</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -2216,47 +2210,43 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>L42-3</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.44147</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.44147</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 22m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 22m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 22m</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 22m</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -2265,6 +2255,426 @@
       <c r="AX7" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 9:53 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344654</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Adhikari</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Adhikari</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9841364306</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 09:53:26 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9828965079</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:05:43 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 09:53:26 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.76123</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Rammandir Hattigauda Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>18:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L38-5</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.34362</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 47m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 9:55 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344750</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Rimesh chaudhary</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Rimesh chaudhary</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9801543414</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 09:55:44 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9801543414</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:10:03 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 09:55:44 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Orchid International College - Private college Maiti Nepal - Bijay Chowk Behind Prayag Marg Kathmand</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>rimeshcdry45@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>17:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L39-5</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 45m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -875,7 +875,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -2325,10 +2325,8 @@
           <t>Prakash Adhikari</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9841364306</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9841364306</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2343,10 +2341,8 @@
       </c>
       <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="inlineStr"/>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>9828965079</t>
-        </is>
+      <c r="U8" s="3" t="n">
+        <v>9828965079</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -2363,10 +2359,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.76123</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.76123</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2418,25 +2412,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L38-5</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.34362</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.34362</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2537,10 +2527,8 @@
           <t>Rimesh chaudhary</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9801543414</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9801543414</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2555,10 +2543,8 @@
       </c>
       <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>9801543414</t>
-        </is>
+      <c r="U9" s="3" t="n">
+        <v>9801543414</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -2630,10 +2616,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2644,7 +2628,7 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -550,32 +550,50 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>62.5%</t>
+      <c r="B5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -646,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -657,10 +675,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -669,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -680,19 +698,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>60.0%</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -707,13 +725,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -734,6 +753,11 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -750,8 +774,11 @@
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>5</v>
+      <c r="D2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -764,10 +791,13 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -782,7 +812,10 @@
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -798,7 +831,10 @@
       <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -812,10 +848,13 @@
         <v>2</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -829,11 +868,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX9"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -869,13 +908,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -2662,6 +2701,438 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:23 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346062</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Binod Pokharel</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Binod Pokharel</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9851003008</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:23:50 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9851003008</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 01:22:17 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:23:50 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.759124</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Near to Morgan Int´l School,Q84M+JRG, Budhanilkantha 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>binodpkhrl9@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>07:01 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Ghimire</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L11-5</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.336243</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>21h 1m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:29 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342696</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Reba Prasad Upreti</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Reba Prasad Upreti</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9849916356</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 04:27:02 PM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9851192713</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 04:27:02 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:29:52 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.694594</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>kalaki  kathmandu, , ,</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>cementricgates@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>10:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>3,7</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.279456</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>3d 18h 2m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>3d 18h 2m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,72 +528,108 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Chandramani Tharu</t>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B7" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>70.0%</t>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -652,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -687,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
     </row>
@@ -698,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>6</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -725,14 +761,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -743,20 +781,30 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -769,16 +817,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>6</v>
+      <c r="F2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -791,12 +845,18 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -810,12 +870,18 @@
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -829,32 +895,69 @@
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>10</v>
+      <c r="F7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -868,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AX16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -881,23 +984,23 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="39" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="39" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="21" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
@@ -2768,10 +2871,8 @@
           <t>Binod Pokharel</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9851003008</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9851003008</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2786,10 +2887,8 @@
       </c>
       <c r="S10" s="3" t="inlineStr"/>
       <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>9851003008</t>
-        </is>
+      <c r="U10" s="3" t="n">
+        <v>9851003008</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -2806,10 +2905,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.759124</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.759124</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2865,25 +2962,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>L11-5</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.336243</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.336243</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2984,10 +3077,8 @@
           <t>Reba Prasad Upreti</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9849916356</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9849916356</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3002,10 +3093,8 @@
       </c>
       <c r="S11" s="3" t="inlineStr"/>
       <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>9851192713</t>
-        </is>
+      <c r="U11" s="3" t="n">
+        <v>9851192713</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -3022,10 +3111,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.694594</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.694594</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -3081,47 +3168,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>3,7</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.279456</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.279456</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>3d 18h 2m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>3d 18h 2m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS11" s="3" t="inlineStr">
-        <is>
-          <t>3d 18h 2m</t>
-        </is>
-      </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>3d 18h 2m</t>
-        </is>
-      </c>
-      <c r="AU11" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV11" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW11" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -3130,6 +3213,1066 @@
       <c r="AX11" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:41 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344784</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Umesh Bhandari</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Umesh Bhandari</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9843081060</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:41:02 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9851148982</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:40:58 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:41:02 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.69939</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Gothatar, Bistagaun 7, Kageshwori Manohara 44600 near THE Food Gallery, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>mshbhndr@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>18:01 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L55-2</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.38381</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:35 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Router Issue</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346160</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Kapali</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Kapali</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9810171425</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:35:04 AM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9810171425</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 02:37:19 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:35:04 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.710676</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Near New Zenith English School, Dhalko, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>prakashkapali21@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>05:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>CDB122</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.302937</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>19h 57m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:36 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344804</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Gorkha hydro and engineering Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Gorkha hydro and engineering Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9862905906</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:56:34 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9841771003</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:56:34 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:36:53 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Buddhanagar-10, Bera Cafe, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>gh.enginnering@hotmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 40m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 40m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:35 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345215</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjaya Dhakal</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjaya Dhakal</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9869179735</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 06:44:23 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>CHB9869179735</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 06:44:23 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:35:01 AM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>27.69890030745179,85.3514402124555, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>sanju111dhala@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>L55-1</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>1d 15h 50m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>1d 15h 50m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:43 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344570</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Ruplal Gyawali</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Ruplal Gyawali</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9868264272</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:43:36 AM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9868264272</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 10:11:55 AM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:43:45 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.670915</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>near by Dream Garden Resort - Family restaurant Budhanilkantha 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>gyawaliruplal80@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>20:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L42-3</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.44147</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>2d 31m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.6%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>17.6%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>3</v>
@@ -832,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>7</v>
@@ -957,7 +957,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX16"/>
+  <dimension ref="A1:AX18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -982,7 +982,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="39" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -3283,10 +3283,8 @@
           <t>Umesh Bhandari</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9843081060</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9843081060</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3321,10 +3319,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.69939</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.69939</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3380,25 +3376,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L55-2</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.38381</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.38381</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3499,10 +3491,8 @@
           <t>Prakash Kapali</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9810171425</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9810171425</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3537,10 +3527,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.710676</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.710676</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3578,10 +3566,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH13" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH13" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
@@ -3600,25 +3586,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>CDB122</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.302937</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.302937</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Issue  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3719,10 +3701,8 @@
           <t>Gorkha hydro and engineering Pvt Ltd</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9862905906</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9862905906</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3808,10 +3788,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
@@ -3822,7 +3800,7 @@
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3923,10 +3901,8 @@
           <t>Sanjaya Dhakal</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9869179735</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9869179735</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -4012,10 +3988,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
@@ -4026,7 +4000,7 @@
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -4127,10 +4101,8 @@
           <t>Ruplal Gyawali</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9868264272</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9868264272</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4165,10 +4137,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.670915</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.670915</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -4224,55 +4194,483 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>L42-3</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.44147</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.44147</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>2d 31m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS16" s="3" t="inlineStr">
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:53 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343091</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Rashmi Tuladhar</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Rashmi Tuladhar</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9841724979</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 09:23:18 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9841724979</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 09:23:18 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:53:59 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.70945</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>near Annapurna Secondary School,ganesthan kathmandu-27, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>nirajmanandhar01@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>06:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.31289</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>3d 13h 30m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>3d 13h 30m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:47 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344547</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Bibhaya Paudel</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Bibhaya Paudel</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9763204623</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:47:47 AM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9843033061</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:57:56 AM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:47:47 AM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.70023</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Anamnagar, Asian Public School, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>bibhaya146@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>20:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>CDB583</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.3296</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT16" s="3" t="inlineStr">
-        <is>
-          <t>2d 31m</t>
-        </is>
-      </c>
-      <c r="AU16" s="3" t="inlineStr">
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>2d 49m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV16" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW16" s="3" t="inlineStr">
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX16" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -1017,7 +1017,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -4309,10 +4309,8 @@
           <t>Rashmi Tuladhar</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9841724979</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9841724979</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4347,10 +4345,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.70945</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.70945</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -4406,25 +4402,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.31289</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.31289</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4525,10 +4517,8 @@
           <t>Bibhaya Paudel</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9763204623</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9763204623</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4563,10 +4553,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.70023</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.70023</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -4622,25 +4610,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>CDB583</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.3296</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.3296</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -863,7 +863,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -888,7 +888,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -913,17 +913,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -936,28 +936,53 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E7" s="4" t="n">
+      <c r="D8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>16</v>
+      <c r="G8" s="4" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -971,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX18"/>
+  <dimension ref="A1:AX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -982,14 +1007,14 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="31" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="39" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="39" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -999,7 +1024,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="21" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
@@ -1017,7 +1042,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -4658,6 +4683,214 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:26 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : frquently disconnected issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>frquently disconnected issue</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342620</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Neupane</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Neupane</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9847329472</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:26:09 AM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>KLK9816451459</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 03:57:23 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:26:09 AM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>Frequent Internet Disconnection</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>QFX Cinemas, City Square Mall QFX Cinemas, City Square Mall - Movie theater P8P9+549 ???????? ??????</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>9816451459@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Due to Optical Power flapping</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>11:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L55-1</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : frquently disconnected issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>3d 19h 28m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : frquently disconnected issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -564,50 +564,50 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -616,20 +616,38 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>72.2%</t>
+      <c r="B8" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -688,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
@@ -723,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
@@ -734,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -761,16 +779,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -791,20 +810,25 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -817,22 +841,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -848,15 +875,18 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -873,15 +903,18 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -898,15 +931,18 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -923,15 +959,18 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -956,7 +995,10 @@
       <c r="F7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -967,22 +1009,25 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>5</v>
       </c>
       <c r="D8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>17</v>
+        <v>2</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX19"/>
+  <dimension ref="A1:AX27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1019,7 +1064,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -1036,7 +1081,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -4750,10 +4795,8 @@
           <t>Prakash Neupane</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9847329472</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9847329472</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4843,10 +4886,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -4857,37 +4898,1637 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>3d 19h 28m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
           <t>Case : frquently disconnected issue  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS19" s="3" t="inlineStr">
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:31 AM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341465</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>samrat shrestha</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>samrat shrestha</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9820084508</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:23:23 AM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>KLK9813561196</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 03:17:02 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:31:00 AM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Dhumbakhel Youth Club - Youth club P852+7J3 ??????? ????? Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>samshrestha080@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>CDB348</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 7m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>4d 20h 13m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:01 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345486</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Chandan shrestha</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Chandan shrestha</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9849210578</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 07:39:04 AM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9818108774</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 07:39:04 AM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:01:45 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.73385</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Banasthali Kharibot opposite of Ballchi Dhurbe Futsal Ground, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>shresthachandan99@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>12:01 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>CDB436</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.29008</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 22m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 22m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:53 AM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344535</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>SUMAN THAPA</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>SUMAN THAPA</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9841514482</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:53:42 AM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9841514482</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:50:07 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:53:42 AM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.687219</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Lord Buddha English Sec. School Details from Google Maps M9QQ+7GG, Madhyapur Thimi 44600 +977 1-6633</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>st4279034@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>21:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>L39-8</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.389849</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>3d 19h 28m</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 3m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>Case : frquently disconnected issue  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW19" s="3" t="inlineStr">
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX19" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:32 AM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345700</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Awasar Khatiwada</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Awasar Khatiwada</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9840225643</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:32:40 AM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9840225643</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 10:06:19 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:32:40 AM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>National Examinations Board - Board of education Madhyapur Thimi Municipality 44811 Madhyapur Thimi</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>awasarkhatiwada@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>11:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>L60-2</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 26m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:07 AM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344549</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Haushala Nirman Sewa Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Haushala Nirman Sewa Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9851139926</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:07:26 AM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>haushalanirmansewa_fttx</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:58:51 AM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:07:26 AM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.68748</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur Road 16, Kathmandu 44600 near Machhapuchchhre Bank Limited, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>kcanuraj1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>21:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>L17-2</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.36292</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 8m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:58 AM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345974</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Sachin Lama</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Sachin Lama</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9845353156</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:58:49 AM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9845353156</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 12:23:32 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:58:49 AM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.66494</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Lagankhel Satbdobato Road -12, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>sachinlama2003@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>09:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.32406</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>23h 35m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:57 AM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr"/>
+      <c r="O26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr"/>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr"/>
+      <c r="V26" s="3" t="inlineStr"/>
+      <c r="W26" s="3" t="inlineStr"/>
+      <c r="X26" s="3" t="inlineStr"/>
+      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="inlineStr"/>
+      <c r="AA26" s="3" t="inlineStr"/>
+      <c r="AB26" s="3" t="inlineStr"/>
+      <c r="AC26" s="3" t="inlineStr"/>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr"/>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr"/>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr"/>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr"/>
+      <c r="AM26" s="3" t="inlineStr"/>
+      <c r="AN26" s="3" t="inlineStr"/>
+      <c r="AO26" s="3" t="inlineStr"/>
+      <c r="AP26" s="3" t="inlineStr"/>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:06 AM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344297</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Raju Lama</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Raju Lama</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9818751954</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:06:43 AM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9818751954</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 09:45:13 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:06:43 AM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.668914</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Jawalakhel Near Alka Hospital 2 wing 2 Ekantakuna, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>yoztmg@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>21:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>CDB122</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.309675</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>2d 13h 21m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>72.4%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>20.7%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>3</v>
@@ -856,10 +856,10 @@
         <v>4</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -1015,7 +1015,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>8</v>
@@ -1024,10 +1024,10 @@
         <v>4</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX27"/>
+  <dimension ref="A1:AX30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4999,10 +4999,8 @@
           <t>samrat shrestha</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9820084508</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9820084508</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -5088,10 +5086,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
@@ -5102,7 +5098,7 @@
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -5203,10 +5199,8 @@
           <t>Chandan shrestha</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9849210578</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9849210578</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -5241,10 +5235,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.73385</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.73385</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -5300,25 +5292,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>CDB436</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.29008</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.29008</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -5409,20 +5397,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M22" s="3" t="inlineStr"/>
       <c r="N22" s="3" t="inlineStr">
         <is>
           <t>SUMAN THAPA</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9841514482</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9841514482</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5457,10 +5439,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.687219</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.687219</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -5516,25 +5496,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>L39-8</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.389849</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.389849</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -5635,10 +5611,8 @@
           <t>Awasar Khatiwada</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9840225643</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9840225643</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5728,10 +5702,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
@@ -5742,7 +5714,7 @@
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5843,10 +5815,8 @@
           <t>Haushala Nirman Sewa Pvt. Ltd</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9851139926</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9851139926</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5881,10 +5851,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.68748</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.68748</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5940,25 +5908,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>L17-2</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.36292</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.36292</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -6059,10 +6023,8 @@
           <t>Sachin Lama</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9845353156</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9845353156</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -6097,10 +6059,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.66494</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.66494</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -6156,25 +6116,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.32406</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.32406</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -6383,10 +6339,8 @@
           <t>Raju Lama</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9818751954</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9818751954</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -6421,10 +6375,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.668914</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.668914</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -6480,53 +6432,681 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>CDB122</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.309675</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.309675</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>2d 13h 21m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS27" s="3" t="inlineStr">
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:02 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345533</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Shreejan Shrestha</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Shreejan Shrestha</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9860104756</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 08:26:28 AM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>9860104756</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 08:26:28 AM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:02:54 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>27.72642</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Nursery Chowk, Dhungedhara, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>shreejanshr@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>12:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>4,1</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>85.29186</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 36m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 36m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:15 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344273</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Chhori Maya Prajapati</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Chhori Maya Prajapati</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9849502962</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:15:33 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9849502962</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 09:11:16 PM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:15:33 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.67875</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>UN Park Alko ward no 11 office, NIC Bank Building, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>niroj1978@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>22:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>CDB064</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.32534</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT27" s="3" t="inlineStr">
-        <is>
-          <t>2d 13h 21m</t>
-        </is>
-      </c>
-      <c r="AU27" s="3" t="inlineStr">
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>2d 15h 4m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV27" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW27" s="3" t="inlineStr">
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX27" s="3" t="inlineStr">
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:06 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344007</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Avash Shrestha</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Avash Shrestha</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9843768014</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:06:10 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9843768014</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 04:47:22 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:06:10 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur Patna	Agnisala, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>3,16</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 18m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>5.6%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>52.8%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -847,7 +847,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>3</v>
@@ -859,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -884,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -921,11 +921,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -977,11 +977,11 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -1003,31 +1003,59 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" s="4" t="n">
+      <c r="B9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>27</v>
+      <c r="G9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX30"/>
+  <dimension ref="A1:AX37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6547,10 +6575,8 @@
           <t>Shreejan Shrestha</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9860104756</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9860104756</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -6585,10 +6611,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>27.72642</t>
-        </is>
+      <c r="Y28" s="3" t="n">
+        <v>27.72642</v>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
@@ -6644,25 +6668,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
           <t>4,1</t>
         </is>
       </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>85.29186</t>
-        </is>
+      <c r="AP28" s="3" t="n">
+        <v>85.29186</v>
       </c>
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -6763,10 +6783,8 @@
           <t>Chhori Maya Prajapati</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9849502962</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9849502962</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6801,10 +6819,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.67875</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.67875</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -6860,25 +6876,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>CDB064</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.32534</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.32534</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -6979,10 +6991,8 @@
           <t>Avash Shrestha</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9843768014</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9843768014</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -7064,10 +7074,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -7078,37 +7086,1537 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 18m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS30" s="3" t="inlineStr">
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:21 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344823</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Man Shrestha</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Man Shrestha</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9843807409</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:21:47 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9849669368</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 01:20:51 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:21:47 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>27.67556</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Khachhen, 16, Shakyai Unique emporium nearby, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>sarojmansh@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>85.32319</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT30" s="3" t="inlineStr">
-        <is>
-          <t>2d 19h 18m</t>
-        </is>
-      </c>
-      <c r="AU30" s="3" t="inlineStr">
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV30" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW30" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX30" s="3" t="inlineStr">
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:19 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>IP TV not Working</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343062</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Magar</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Magar</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9813664152</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 08:43:35 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9813664152</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:56:52 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:19:10 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.70515</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>P842+3W9, ???????: ?????, Kathmandu 44600 near Paropakar Furniture, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>sabinmagar4152@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>General Query &amp; Feedback</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>08:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr"/>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>4,11</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.302205</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>2d 15h 35m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>3d 15h 22m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:18 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>IP TV not Working</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343062</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Magar</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Magar</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9813664152</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 08:43:35 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9813664152</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:56:52 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:19:10 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.70515</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>P842+3W9, ???????: ?????, Kathmandu 44600 near Paropakar Furniture, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>sabinmagar4152@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>General Query &amp; Feedback</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>08:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr"/>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>4,11</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.302205</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>2d 15h 35m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>3d 15h 22m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:25 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Red light in stb  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Red light in stb</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344730</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Kishan Thapa</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Kishan Thapa</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9841306366</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:08:43 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9841306366</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:54:56 AM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:25:08 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.741487</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Trishuli Hwy, Tarakeshwar,Near by Kantipur AB Party Palace, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr"/>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>20:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>L30-6</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.308317</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Red light in stb  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>2d 16m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>2d 30m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Red light in stb  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:24 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Red light in stb  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Red light in stb</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344730</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Kishan Thapa</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Kishan Thapa</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9841306366</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:08:43 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9841306366</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:54:56 AM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:25:08 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>27.741487</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Trishuli Hwy, Tarakeshwar,Near by Kantipur AB Party Palace, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr"/>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>20:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>L30-6</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>85.308317</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Red light in stb  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>2d 16m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>2d 30m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Red light in stb  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:19 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light in stb  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>No light in stb</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345189</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Ram chandra dhungana</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Ram chandra dhungana</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9802000651</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 06:55:04 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>KLK9802000651</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 06:10:23 PM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:19:12 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>ktm soyambhu  sanobharayang, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>chandra85@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>14:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>CDB532</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr"/>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light in stb  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 24m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 8m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light in stb  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:18 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light in stb  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>No light in stb</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345189</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Ram chandra dhungana</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Ram chandra dhungana</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9802000651</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 06:55:04 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>KLK9802000651</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 06:10:23 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:19:12 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>ktm soyambhu  sanobharayang, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>chandra85@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>14:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>CDB532</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr"/>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light in stb  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 24m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 8m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : No light in stb  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>75.7%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>37.8%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.4%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>51.4%</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>2</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>5</v>
@@ -1055,7 +1055,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX37"/>
+  <dimension ref="A1:AX38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7187,10 +7187,8 @@
           <t>Saroj Man Shrestha</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9843807409</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9843807409</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -7225,10 +7223,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>27.67556</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>27.67556</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -7280,25 +7276,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>85.32319</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>85.32319</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -7399,10 +7391,8 @@
           <t>Sabin Magar</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9813664152</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9813664152</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -7437,10 +7427,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.70515</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.70515</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -7496,25 +7484,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>4,11</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.302205</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.302205</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
@@ -7615,10 +7599,8 @@
           <t>Sabin Magar</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9813664152</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9813664152</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7653,10 +7635,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>27.70515</t>
-        </is>
+      <c r="Y33" s="3" t="n">
+        <v>27.70515</v>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
@@ -7712,25 +7692,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>4,11</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.302205</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.302205</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : IP TV not Working   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -7831,10 +7807,8 @@
           <t>Kishan Thapa</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9841306366</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9841306366</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7869,10 +7843,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.741487</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.741487</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -7906,10 +7878,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH34" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH34" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
@@ -7928,25 +7898,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>L30-6</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.308317</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.308317</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : Red light in stb  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -8047,10 +8013,8 @@
           <t>Kishan Thapa</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9841306366</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9841306366</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -8085,10 +8049,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>27.741487</t>
-        </is>
+      <c r="Y35" s="3" t="n">
+        <v>27.741487</v>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
@@ -8122,10 +8084,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH35" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH35" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
@@ -8144,25 +8104,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>L30-6</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>85.308317</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>85.308317</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : Red light in stb  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -8263,10 +8219,8 @@
           <t>Ram chandra dhungana</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9802000651</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9802000651</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -8338,10 +8292,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH36" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH36" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
@@ -8360,10 +8312,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
@@ -8374,7 +8324,7 @@
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : No light in stb  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -8475,10 +8425,8 @@
           <t>Ram chandra dhungana</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9802000651</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9802000651</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -8550,10 +8498,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH37" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH37" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
@@ -8572,10 +8518,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
@@ -8586,29 +8530,29 @@
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 24m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 8m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
           <t>Case : No light in stb  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>1d 17h 24m</t>
-        </is>
-      </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>1d 18h 8m</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV37" s="3" t="inlineStr">
-        <is>
-          <t>Case : No light in stb  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -8617,6 +8561,226 @@
       <c r="AX37" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:37 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Red light in stb   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Red light in stb</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343792</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Abrar Ahmad</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Abrar Ahmad</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9803808220</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:37:30 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9803808220</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 02:05:48 PM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:37:30 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.696567</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>M7WW+MWJ,  Kathmandu 44600 Near by 	Kuleshwor Kathmandu Campus, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>ahmadabarar2@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>04:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB386</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>85.296854</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Red light in stb   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 31m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Red light in stb   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>70.7%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>36.6%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>4.9%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>5</v>
@@ -859,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -1040,7 +1040,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>5</v>
@@ -1055,7 +1055,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX38"/>
+  <dimension ref="A1:AX42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8631,10 +8631,8 @@
           <t>Abrar Ahmad</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9803808220</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9803808220</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -8669,10 +8667,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>27.696567</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>27.696567</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -8710,10 +8706,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH38" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH38" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
@@ -8732,55 +8726,583 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>CDB386</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>85.296854</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>85.296854</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 31m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
           <t>Case : Red light in stb   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS38" s="3" t="inlineStr">
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:58 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr"/>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr"/>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr"/>
+      <c r="V39" s="3" t="inlineStr"/>
+      <c r="W39" s="3" t="inlineStr"/>
+      <c r="X39" s="3" t="inlineStr"/>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr"/>
+      <c r="AA39" s="3" t="inlineStr"/>
+      <c r="AB39" s="3" t="inlineStr"/>
+      <c r="AC39" s="3" t="inlineStr"/>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr"/>
+      <c r="AF39" s="3" t="inlineStr"/>
+      <c r="AG39" s="3" t="inlineStr"/>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr"/>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr"/>
+      <c r="AM39" s="3" t="inlineStr"/>
+      <c r="AN39" s="3" t="inlineStr"/>
+      <c r="AO39" s="3" t="inlineStr"/>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:59 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr"/>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr"/>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr"/>
+      <c r="V40" s="3" t="inlineStr"/>
+      <c r="W40" s="3" t="inlineStr"/>
+      <c r="X40" s="3" t="inlineStr"/>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr"/>
+      <c r="AA40" s="3" t="inlineStr"/>
+      <c r="AB40" s="3" t="inlineStr"/>
+      <c r="AC40" s="3" t="inlineStr"/>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr"/>
+      <c r="AF40" s="3" t="inlineStr"/>
+      <c r="AG40" s="3" t="inlineStr"/>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr"/>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr"/>
+      <c r="AM40" s="3" t="inlineStr"/>
+      <c r="AN40" s="3" t="inlineStr"/>
+      <c r="AO40" s="3" t="inlineStr"/>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 1:00 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi -6 router instal   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr"/>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr"/>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr"/>
+      <c r="V41" s="3" t="inlineStr"/>
+      <c r="W41" s="3" t="inlineStr"/>
+      <c r="X41" s="3" t="inlineStr"/>
+      <c r="Y41" s="3" t="inlineStr"/>
+      <c r="Z41" s="3" t="inlineStr"/>
+      <c r="AA41" s="3" t="inlineStr"/>
+      <c r="AB41" s="3" t="inlineStr"/>
+      <c r="AC41" s="3" t="inlineStr"/>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr"/>
+      <c r="AF41" s="3" t="inlineStr"/>
+      <c r="AG41" s="3" t="inlineStr"/>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr"/>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr"/>
+      <c r="AM41" s="3" t="inlineStr"/>
+      <c r="AN41" s="3" t="inlineStr"/>
+      <c r="AO41" s="3" t="inlineStr"/>
+      <c r="AP41" s="3" t="inlineStr"/>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi -6 router instal   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:59 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgarde   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgarde</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345172</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Bibek Shah</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Bibek Shah</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9702676935</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:59:23 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>CHB9702676935</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 05:53:25 PM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:59:23 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr"/>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>near by Fitness Hut - Gym Prayag Marg Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>9815897561@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>15:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>L3-1</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr"/>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgarde   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>2d 22h 31m</t>
-        </is>
-      </c>
-      <c r="AU38" s="3" t="inlineStr">
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 5m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV38" s="3" t="inlineStr">
-        <is>
-          <t>Case : Red light in stb   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW38" s="3" t="inlineStr">
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgarde   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX38" s="3" t="inlineStr">
-        <is>
-          <t>Ajit Shrestha</t>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>66.0%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.2%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>4.3%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.9%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -844,7 +844,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>5</v>
@@ -853,13 +853,13 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -893,11 +893,11 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -921,11 +921,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>General Query &amp; Feedback</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -1005,17 +1005,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -1031,31 +1031,59 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="E10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>33</v>
+      <c r="H10" s="4" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX42"/>
+  <dimension ref="A1:AX48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9165,10 +9193,8 @@
           <t>Bibek Shah</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9702676935</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9702676935</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -9258,10 +9284,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
@@ -9272,35 +9296,1307 @@
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 5m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgarde   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS42" s="3" t="inlineStr">
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:55 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346391</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Karma wangal lama</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Karma wangal lama</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9803876548</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:14:41 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9803876548</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:56:17 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:14:41 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu 44600 near by Shiva Mandir, Patitar - Hindu temple, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>sabaikoid@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>05:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Rabindra Bohora</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>L49-3</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT42" s="3" t="inlineStr">
-        <is>
-          <t>1d 19h 5m</t>
-        </is>
-      </c>
-      <c r="AU42" s="3" t="inlineStr">
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>20h 18m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:54 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346391</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Karma wangal lama</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Karma wangal lama</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9803876548</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:14:41 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9803876548</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:56:17 PM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:14:41 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu 44600 near by Shiva Mandir, Patitar - Hindu temple, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>sabaikoid@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>05:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Rabindra Bohora</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>L49-3</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>20h 18m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX44" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 1:16 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : adapter issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>adapter issue</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345446</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Bimala Gurung</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Bimala Gurung</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9806838503</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:16:43 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9806838503</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 06:46:45 AM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:16:43 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.66936</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur,Dholality Prachanda Niwas , Near Bigmart, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>gurungbimala200@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>13:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>4,11</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.3244</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : adapter issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 29m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV42" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgarde   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW42" s="3" t="inlineStr">
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : adapter issue   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX42" s="3" t="inlineStr">
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 1:16 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346405</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Dipesh Shrestha</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Dipesh Shrestha</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9841650647</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:16:12 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9841650647</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:59:38 PM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:16:12 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>27.68923</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Near to Jaya Ganesh Mandir , Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>dipestha27@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>06:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>L14-1</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>85.35072</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>20h 16m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 1:03 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345215</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Sanjaya Dhakal</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Sanjaya Dhakal</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9869179735</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:03:17 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>CHB9869179735</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 06:44:23 PM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:03:17 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr"/>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>27.69890030745179,85.3514402124555, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>sanju111dhala@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr"/>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>L55-1</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr"/>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 18m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 1:02 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344804</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Gorkha hydro and engineering Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Gorkha hydro and engineering Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9862905906</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:02:15 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9841771003</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 12:56:34 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:02:15 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr"/>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Buddhanagar-10, Bera Cafe, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>gh.enginnering@hotmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr"/>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr"/>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>2d 5m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>31</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>62.0%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>34.0%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>15</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
     </row>
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>3</v>
@@ -859,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>7</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>8</v>
@@ -1083,7 +1083,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX48"/>
+  <dimension ref="A1:AX51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9397,10 +9397,8 @@
           <t>Karma wangal lama</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9803876548</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9803876548</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -9435,10 +9433,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -9494,25 +9490,21 @@
           <t>Rabindra Bohora</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>L49-3</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
@@ -9613,10 +9605,8 @@
           <t>Karma wangal lama</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9803876548</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9803876548</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -9651,10 +9641,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -9710,25 +9698,21 @@
           <t>Rabindra Bohora</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>L49-3</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -9829,10 +9813,8 @@
           <t>Bimala Gurung</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9806838503</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9806838503</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -9867,10 +9849,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.66936</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.66936</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -9926,25 +9906,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>4,11</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.3244</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.3244</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : adapter issue   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
@@ -10045,10 +10021,8 @@
           <t>Dipesh Shrestha</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9841650647</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9841650647</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -10083,10 +10057,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>27.68923</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v>27.68923</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -10142,25 +10114,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>L14-1</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>85.35072</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>85.35072</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
@@ -10261,10 +10229,8 @@
           <t>Sanjaya Dhakal</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9869179735</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9869179735</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -10350,10 +10316,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
@@ -10364,7 +10328,7 @@
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
@@ -10465,10 +10429,8 @@
           <t>Gorkha hydro and engineering Pvt Ltd</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9862905906</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9862905906</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -10554,10 +10516,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
@@ -10568,37 +10528,665 @@
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>2d 5m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS48" s="3" t="inlineStr">
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 1:30 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343902</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Mira Giri</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Mira Giri</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9813940809</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:25:58 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9813940809</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 03:25:58 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:30:00 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr"/>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Jana Marg 2 Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>9813940809@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr"/>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr"/>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 4m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 4m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 1:22 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347020</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Raju Lama</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Raju Lama</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9848047877</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:22:35 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9848047877</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:34:04 AM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:22:35 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.67412</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Near Mount Hermoun School, Chyasal chowk , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr"/>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr"/>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>2,8</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.32794</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>2d 5m</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>2h 48m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV48" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW48" s="3" t="inlineStr">
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX48" s="3" t="inlineStr">
-        <is>
-          <t>Chandramani Tharu</t>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 1:28 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346391</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Karma wangal lama</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Karma wangal lama</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9803876548</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:14:41 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9803876548</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:56:17 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:28:19 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu 44600 near by Shiva Mandir, Patitar - Hindu temple, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>sabaikoid@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>05:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L49-3</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>13m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>20h 32m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>31.5%</t>
         </is>
       </c>
     </row>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>53.7%</t>
         </is>
       </c>
     </row>
@@ -853,13 +853,13 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -884,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -1077,13 +1077,13 @@
         <v>8</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX51"/>
+  <dimension ref="A1:AX55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10629,10 +10629,8 @@
           <t>Mira Giri</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9813940809</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9813940809</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -10718,10 +10716,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
@@ -10732,7 +10728,7 @@
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -10833,10 +10829,8 @@
           <t>Raju Lama</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9848047877</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9848047877</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -10871,10 +10865,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.67412</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.67412</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -10922,25 +10914,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>2,8</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.32794</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.32794</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
@@ -11041,10 +11029,8 @@
           <t>Karma wangal lama</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9803876548</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9803876548</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -11079,10 +11065,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y51" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z51" s="3" t="inlineStr">
         <is>
@@ -11138,47 +11122,43 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
           <t>L49-3</t>
         </is>
       </c>
-      <c r="AP51" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>13m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>20h 32m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS51" s="3" t="inlineStr">
-        <is>
-          <t>13m</t>
-        </is>
-      </c>
-      <c r="AT51" s="3" t="inlineStr">
-        <is>
-          <t>20h 32m</t>
-        </is>
-      </c>
-      <c r="AU51" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV51" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW51" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -11187,6 +11167,850 @@
       <c r="AX51" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 1:40 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347212</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Sujata Bhusal</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Sujata Bhusal</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9840306008</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:40:33 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>9840306008</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 12:34:51 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:40:33 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.7394</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Kapan Marg, Mandikhatar,opposite to Sashi dai ko pasal, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr"/>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>01:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Shristi Shrestha</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>L21-1</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.34673</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>1h 5m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX52" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 1:37 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346987</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Biju Shahi</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Biju Shahi</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9851321351</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:37:13 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>CHB9851321351</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:09:52 AM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:37:13 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr"/>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>Swarna Shiksha English Secondary School - School P9RQ+HF2 Gokarneshwor 44600, Kathmandu, Nepal, Nepa</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>03:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>L1-CDB7</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr"/>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>3h 27m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 1:34 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : RED LIGHT IPTV  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>RED LIGHT IPTV</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345328</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Shrestha</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Shrestha</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9818815777</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 08:44:00 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>9818815777</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 08:42:15 PM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:34:19 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr">
+        <is>
+          <t>27.72209</t>
+        </is>
+      </c>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>Panchdhara Near Kamala beauty parlor , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr"/>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr">
+        <is>
+          <t>13:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr">
+        <is>
+          <t>85.27905</t>
+        </is>
+      </c>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : RED LIGHT IPTV  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 50m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 52m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : RED LIGHT IPTV  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX54" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 1:32 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343621</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Shrestha</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Shrestha</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9818815777</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 08:42:31 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9818815777</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 11:52:23 AM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:32:51 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>27.72209</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Panchdhara Near Kamala beauty parlor , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr"/>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>07:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>85.27905</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 50m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 40m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.7%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.5%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>52.7%</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>General Query &amp; Feedback</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -903,7 +903,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -977,11 +977,11 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -1033,11 +1033,11 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -1071,7 +1071,7 @@
         <v>7</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>8</v>
@@ -1083,7 +1083,7 @@
         <v>7</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX55"/>
+  <dimension ref="A1:AX56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11237,10 +11237,8 @@
           <t>Sujata Bhusal</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9840306008</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9840306008</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -11275,10 +11273,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.7394</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.7394</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -11330,25 +11326,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>L21-1</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>85.34673</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>85.34672999999999</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
@@ -11449,10 +11441,8 @@
           <t>Biju Shahi</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9851321351</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9851321351</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -11542,10 +11532,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
@@ -11556,7 +11544,7 @@
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
@@ -11657,10 +11645,8 @@
           <t>Sabin Shrestha</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9818815777</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9818815777</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -11695,10 +11681,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y54" s="3" t="inlineStr">
-        <is>
-          <t>27.72209</t>
-        </is>
+      <c r="Y54" s="3" t="n">
+        <v>27.72209</v>
       </c>
       <c r="Z54" s="3" t="inlineStr">
         <is>
@@ -11750,25 +11734,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="AP54" s="3" t="inlineStr">
-        <is>
-          <t>85.27905</t>
-        </is>
+      <c r="AP54" s="3" t="n">
+        <v>85.27905</v>
       </c>
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : RED LIGHT IPTV  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -11869,10 +11849,8 @@
           <t>Sabin Shrestha</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9818815777</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9818815777</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -11907,10 +11885,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y55" s="3" t="inlineStr">
-        <is>
-          <t>27.72209</t>
-        </is>
+      <c r="Y55" s="3" t="n">
+        <v>27.72209</v>
       </c>
       <c r="Z55" s="3" t="inlineStr">
         <is>
@@ -11962,47 +11938,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>85.27905</t>
-        </is>
+      <c r="AP55" s="3" t="n">
+        <v>85.27905</v>
       </c>
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 50m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>3d 1h 40m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS55" s="3" t="inlineStr">
-        <is>
-          <t>1d 16h 50m</t>
-        </is>
-      </c>
-      <c r="AT55" s="3" t="inlineStr">
-        <is>
-          <t>3d 1h 40m</t>
-        </is>
-      </c>
-      <c r="AU55" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV55" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW55" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -12011,6 +11983,222 @@
       <c r="AX55" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 1:51 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5G name not showing   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>5G name not showing</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344712</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Rahul singh</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Rahul singh</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9811619866</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:51:30 PM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>LTP9851067851</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:42:19 AM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 01:51:30 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>Lagankhel, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr">
+        <is>
+          <t>9811619866@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr">
+        <is>
+          <t>22:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>CDB927</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5G name not showing   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 9m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5G name not showing   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX56" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>63.8%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>31.0%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>6.9%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>53.4%</t>
         </is>
       </c>
     </row>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>6</v>
@@ -859,7 +859,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -878,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>3</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -1065,16 +1065,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>7</v>
@@ -1083,7 +1083,7 @@
         <v>7</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX56"/>
+  <dimension ref="A1:AX59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12053,10 +12053,8 @@
           <t>Rahul singh</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9811619866</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9811619866</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -12091,10 +12089,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y56" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z56" s="3" t="inlineStr">
         <is>
@@ -12150,55 +12146,683 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
           <t>CDB927</t>
         </is>
       </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 9m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
           <t>Case : 5G name not showing   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS56" s="3" t="inlineStr">
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX56" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 2:05 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344719</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Rupesh Thakur</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>Rupesh Thakur</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>9823407567</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:45:50 AM</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>CHB9823407567</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:45:50 AM</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 02:05:39 PM</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr"/>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr">
+        <is>
+          <t>Annapurna Sec. School Annapurna Sec. School - Higher secondary school Kathmandu 44600, Bagmati, Nepa</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="inlineStr">
+        <is>
+          <t>9823407567@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="inlineStr"/>
+      <c r="AI57" s="3" t="inlineStr">
+        <is>
+          <t>22:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>CDB271</t>
+        </is>
+      </c>
+      <c r="AP57" s="3" t="inlineStr"/>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 19m</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 19m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX57" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 2:10 PM</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346370</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Kumari Nanda Jaiswar Bhatta</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Kumari Nanda Jaiswar Bhatta</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>9818548099</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:48:50 PM</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>9867369591</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:48:50 PM</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 02:10:22 PM</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr">
+        <is>
+          <t>27.68548</t>
+        </is>
+      </c>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr">
+        <is>
+          <t>Madhya Marg, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF58" s="3" t="inlineStr">
+        <is>
+          <t>anshusafalpatel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="inlineStr"/>
+      <c r="AI58" s="3" t="inlineStr"/>
+      <c r="AJ58" s="3" t="inlineStr"/>
+      <c r="AK58" s="3" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>CDB488</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr">
+        <is>
+          <t>85.33084</t>
+        </is>
+      </c>
+      <c r="AQ58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>21h 21m</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>21h 21m</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX58" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 2:04 PM</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>IPTV</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347092</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Pratik Bhattarai</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>Pratik Bhattarai</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>9846718758</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 02:04:56 PM</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>9846718758</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:18:31 AM</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 02:04:56 PM</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr">
+        <is>
+          <t>27.72743</t>
+        </is>
+      </c>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>Gongabu Sarkaridhara, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr">
+        <is>
+          <t>soulzstone@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr"/>
+      <c r="AI59" s="3" t="inlineStr"/>
+      <c r="AJ59" s="3" t="inlineStr"/>
+      <c r="AK59" s="3" t="inlineStr"/>
+      <c r="AL59" s="3" t="inlineStr"/>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>L23-4</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr">
+        <is>
+          <t>85.31201</t>
+        </is>
+      </c>
+      <c r="AQ59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT56" s="3" t="inlineStr">
-        <is>
-          <t>2d 2h 9m</t>
-        </is>
-      </c>
-      <c r="AU56" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV56" s="3" t="inlineStr">
-        <is>
-          <t>Case : 5G name not showing   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW56" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX56" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>2h 46m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX59" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>64.4%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.5%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>7</v>
@@ -859,7 +859,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -1074,7 +1074,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>7</v>
@@ -1083,7 +1083,7 @@
         <v>7</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX59"/>
+  <dimension ref="A1:AX60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12261,10 +12261,8 @@
           <t>Rupesh Thakur</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>9823407567</t>
-        </is>
+      <c r="O57" s="3" t="n">
+        <v>9823407567</v>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
@@ -12354,10 +12352,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN57" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
@@ -12368,7 +12364,7 @@
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
@@ -12469,10 +12465,8 @@
           <t>Kumari Nanda Jaiswar Bhatta</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>9818548099</t>
-        </is>
+      <c r="O58" s="3" t="n">
+        <v>9818548099</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
@@ -12507,10 +12501,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y58" s="3" t="inlineStr">
-        <is>
-          <t>27.68548</t>
-        </is>
+      <c r="Y58" s="3" t="n">
+        <v>27.68548</v>
       </c>
       <c r="Z58" s="3" t="inlineStr">
         <is>
@@ -12562,25 +12554,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN58" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
           <t>CDB488</t>
         </is>
       </c>
-      <c r="AP58" s="3" t="inlineStr">
-        <is>
-          <t>85.33084</t>
-        </is>
+      <c r="AP58" s="3" t="n">
+        <v>85.33083999999999</v>
       </c>
       <c r="AQ58" s="3" t="inlineStr"/>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
@@ -12681,10 +12669,8 @@
           <t>Pratik Bhattarai</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>9846718758</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>9846718758</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
@@ -12719,10 +12705,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y59" s="3" t="inlineStr">
-        <is>
-          <t>27.72743</t>
-        </is>
+      <c r="Y59" s="3" t="n">
+        <v>27.72743</v>
       </c>
       <c r="Z59" s="3" t="inlineStr">
         <is>
@@ -12774,53 +12758,253 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN59" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
           <t>L23-4</t>
         </is>
       </c>
-      <c r="AP59" s="3" t="inlineStr">
-        <is>
-          <t>85.31201</t>
-        </is>
+      <c r="AP59" s="3" t="n">
+        <v>85.31201</v>
       </c>
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>2h 46m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS59" s="3" t="inlineStr">
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX59" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 2:24 PM</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345983</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Ramila KC Gurung</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>Ramila KC Gurung</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>9843451434</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 02:24:27 PM</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>9843451434</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 12:33:07 PM</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 02:24:27 PM</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="inlineStr"/>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA60" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC60" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr"/>
+      <c r="AE60" s="3" t="inlineStr">
+        <is>
+          <t>gangabu ganesh than, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF60" s="3" t="inlineStr"/>
+      <c r="AG60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH60" s="3" t="inlineStr"/>
+      <c r="AI60" s="3" t="inlineStr">
+        <is>
+          <t>11:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ60" s="3" t="inlineStr"/>
+      <c r="AK60" s="3" t="inlineStr"/>
+      <c r="AL60" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>L41-3</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr"/>
+      <c r="AQ60" s="3" t="inlineStr"/>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT59" s="3" t="inlineStr">
-        <is>
-          <t>2h 46m</t>
-        </is>
-      </c>
-      <c r="AU59" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV59" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW59" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX59" s="3" t="inlineStr">
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 51m</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX60" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>29.0%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>8.1%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.8%</t>
         </is>
       </c>
     </row>
@@ -779,10 +779,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -850,16 +850,16 @@
         <v>6</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>7</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -949,11 +949,11 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -977,11 +977,11 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>General Query &amp; Feedback</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -1005,7 +1005,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -1059,31 +1059,59 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" s="4" t="n">
+      <c r="E11" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G10" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>47</v>
+      <c r="G11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX60"/>
+  <dimension ref="A1:AX63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1132,7 +1160,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="31" customWidth="1" min="32" max="32"/>
-    <col width="38" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -12873,10 +12901,8 @@
           <t>Ramila KC Gurung</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>9843451434</t>
-        </is>
+      <c r="O60" s="3" t="n">
+        <v>9843451434</v>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
@@ -12962,10 +12988,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN60" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
@@ -12976,37 +13000,669 @@
       <c r="AQ60" s="3" t="inlineStr"/>
       <c r="AR60" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 51m</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS60" s="3" t="inlineStr">
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX60" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 2:44 PM</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347023</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Shahi</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Shahi</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>9851034046</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 02:44:00 PM</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>9851034046</t>
+        </is>
+      </c>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 10:36:10 AM</t>
+        </is>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 02:44:00 PM</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y61" s="3" t="inlineStr">
+        <is>
+          <t>27.748241</t>
+        </is>
+      </c>
+      <c r="Z61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA61" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB61" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC61" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD61" s="3" t="inlineStr"/>
+      <c r="AE61" s="3" t="inlineStr">
+        <is>
+          <t>Near Aradhana Health Care Center,P8XG+822, Tokha 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF61" s="3" t="inlineStr">
+        <is>
+          <t>bishalshahi2499@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG61" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH61" s="3" t="inlineStr"/>
+      <c r="AI61" s="3" t="inlineStr">
+        <is>
+          <t>04:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ61" s="3" t="inlineStr"/>
+      <c r="AK61" s="3" t="inlineStr"/>
+      <c r="AL61" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM61" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN61" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO61" s="3" t="inlineStr">
+        <is>
+          <t>L11-7</t>
+        </is>
+      </c>
+      <c r="AP61" s="3" t="inlineStr">
+        <is>
+          <t>85.32375</t>
+        </is>
+      </c>
+      <c r="AQ61" s="3" t="inlineStr"/>
+      <c r="AR61" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT60" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 51m</t>
-        </is>
-      </c>
-      <c r="AU60" s="3" t="inlineStr">
+      <c r="AT61" s="3" t="inlineStr">
+        <is>
+          <t>4h 7m</t>
+        </is>
+      </c>
+      <c r="AU61" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV60" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW60" s="3" t="inlineStr">
+      <c r="AV61" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW61" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX60" s="3" t="inlineStr">
+      <c r="AX61" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 2:45 PM</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342919</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>Mission shrestha</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>Mission shrestha</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>9840344764</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="inlineStr"/>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:03:48 PM</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr"/>
+      <c r="T62" s="3" t="inlineStr"/>
+      <c r="U62" s="3" t="inlineStr">
+        <is>
+          <t>9880368739</t>
+        </is>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 06:54:03 PM</t>
+        </is>
+      </c>
+      <c r="W62" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 02:45:02 PM</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y62" s="3" t="inlineStr">
+        <is>
+          <t>27.69903</t>
+        </is>
+      </c>
+      <c r="Z62" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA62" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB62" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC62" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD62" s="3" t="inlineStr"/>
+      <c r="AE62" s="3" t="inlineStr">
+        <is>
+          <t>Near Dahachok, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF62" s="3" t="inlineStr">
+        <is>
+          <t>9880368739@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG62" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH62" s="3" t="inlineStr"/>
+      <c r="AI62" s="3" t="inlineStr"/>
+      <c r="AJ62" s="3" t="inlineStr"/>
+      <c r="AK62" s="3" t="inlineStr"/>
+      <c r="AL62" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN62" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO62" s="3" t="inlineStr">
+        <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="AP62" s="3" t="inlineStr">
+        <is>
+          <t>85.24414</t>
+        </is>
+      </c>
+      <c r="AQ62" s="3" t="inlineStr"/>
+      <c r="AR62" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS62" s="3" t="inlineStr">
+        <is>
+          <t>3d 18h 41m</t>
+        </is>
+      </c>
+      <c r="AT62" s="3" t="inlineStr">
+        <is>
+          <t>3d 19h 50m</t>
+        </is>
+      </c>
+      <c r="AU62" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV62" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 2:35 PM</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344441</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh khadak</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh khadak</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>9766973962</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr"/>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 08:31:15 AM</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="3" t="inlineStr"/>
+      <c r="U63" s="3" t="inlineStr">
+        <is>
+          <t>9766973962</t>
+        </is>
+      </c>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 08:31:15 AM</t>
+        </is>
+      </c>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 02:35:33 PM</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y63" s="3" t="inlineStr"/>
+      <c r="Z63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA63" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB63" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC63" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD63" s="3" t="inlineStr"/>
+      <c r="AE63" s="3" t="inlineStr">
+        <is>
+          <t>Ganeshman Singh Multiple Campus - College M7RM+MW5 Kathmandu 44600 - Kathmandu Metropolitan, Kathman</t>
+        </is>
+      </c>
+      <c r="AF63" s="3" t="inlineStr"/>
+      <c r="AG63" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH63" s="3" t="inlineStr"/>
+      <c r="AI63" s="3" t="inlineStr">
+        <is>
+          <t>00:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ63" s="3" t="inlineStr"/>
+      <c r="AK63" s="3" t="inlineStr"/>
+      <c r="AL63" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM63" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN63" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO63" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP63" s="3" t="inlineStr"/>
+      <c r="AQ63" s="3" t="inlineStr"/>
+      <c r="AR63" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS63" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 4m</t>
+        </is>
+      </c>
+      <c r="AT63" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 4m</t>
+        </is>
+      </c>
+      <c r="AU63" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV63" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW63" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX63" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -1171,7 +1171,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -13101,10 +13101,8 @@
           <t>Bishal Shahi</t>
         </is>
       </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>9851034046</t>
-        </is>
+      <c r="O61" s="3" t="n">
+        <v>9851034046</v>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
@@ -13139,10 +13137,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y61" s="3" t="inlineStr">
-        <is>
-          <t>27.748241</t>
-        </is>
+      <c r="Y61" s="3" t="n">
+        <v>27.748241</v>
       </c>
       <c r="Z61" s="3" t="inlineStr">
         <is>
@@ -13198,25 +13194,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN61" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN61" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
           <t>L11-7</t>
         </is>
       </c>
-      <c r="AP61" s="3" t="inlineStr">
-        <is>
-          <t>85.32375</t>
-        </is>
+      <c r="AP61" s="3" t="n">
+        <v>85.32375</v>
       </c>
       <c r="AQ61" s="3" t="inlineStr"/>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
@@ -13317,10 +13309,8 @@
           <t>Mission shrestha</t>
         </is>
       </c>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
-          <t>9840344764</t>
-        </is>
+      <c r="O62" s="3" t="n">
+        <v>9840344764</v>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
@@ -13355,10 +13345,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y62" s="3" t="inlineStr">
-        <is>
-          <t>27.69903</t>
-        </is>
+      <c r="Y62" s="3" t="n">
+        <v>27.69903</v>
       </c>
       <c r="Z62" s="3" t="inlineStr">
         <is>
@@ -13410,25 +13398,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN62" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN62" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
           <t>1,7</t>
         </is>
       </c>
-      <c r="AP62" s="3" t="inlineStr">
-        <is>
-          <t>85.24414</t>
-        </is>
+      <c r="AP62" s="3" t="n">
+        <v>85.24414</v>
       </c>
       <c r="AQ62" s="3" t="inlineStr"/>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
@@ -13529,10 +13513,8 @@
           <t>Sandesh khadak</t>
         </is>
       </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>9766973962</t>
-        </is>
+      <c r="O63" s="3" t="n">
+        <v>9766973962</v>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
@@ -13618,10 +13600,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN63" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN63" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
@@ -13632,7 +13612,7 @@
       <c r="AQ63" s="3" t="inlineStr"/>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>9</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>40</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>27.7%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>22</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>5</v>
@@ -859,7 +859,7 @@
         <v>5</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>8</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>11</v>
@@ -1111,7 +1111,7 @@
         <v>9</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1125,7 +1125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX63"/>
+  <dimension ref="A1:AX66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1171,7 +1171,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -13646,6 +13646,538 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 2:49 PM</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345296</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Rojan Shrestha</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>Rojan Shrestha</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>9841115011</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr"/>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 02:49:28 PM</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr"/>
+      <c r="T64" s="3" t="inlineStr"/>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>9813880130</t>
+        </is>
+      </c>
+      <c r="V64" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 08:03:40 PM</t>
+        </is>
+      </c>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 02:49:28 PM</t>
+        </is>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y64" s="3" t="inlineStr">
+        <is>
+          <t>27.69531</t>
+        </is>
+      </c>
+      <c r="Z64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA64" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB64" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC64" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD64" s="3" t="inlineStr"/>
+      <c r="AE64" s="3" t="inlineStr">
+        <is>
+          <t>Next to Gita Store,Chhune Marg,Kathmandu, Kathmandu, Bagmati, Central, Nepal, Bagmati, Central, Nepa</t>
+        </is>
+      </c>
+      <c r="AF64" s="3" t="inlineStr">
+        <is>
+          <t>imrozan1849@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH64" s="3" t="inlineStr"/>
+      <c r="AI64" s="3" t="inlineStr"/>
+      <c r="AJ64" s="3" t="inlineStr"/>
+      <c r="AK64" s="3" t="inlineStr"/>
+      <c r="AL64" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM64" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN64" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO64" s="3" t="inlineStr">
+        <is>
+          <t>CDB387</t>
+        </is>
+      </c>
+      <c r="AP64" s="3" t="inlineStr">
+        <is>
+          <t>85.29619</t>
+        </is>
+      </c>
+      <c r="AQ64" s="3" t="inlineStr"/>
+      <c r="AR64" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 45m</t>
+        </is>
+      </c>
+      <c r="AU64" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV64" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW64" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX64" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 3:06 PM</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345365</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>Manan Shrestha</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>Manan Shrestha</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>9849517411</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr"/>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 03:16:47 PM</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr"/>
+      <c r="T65" s="3" t="inlineStr"/>
+      <c r="U65" s="3" t="inlineStr">
+        <is>
+          <t>mananshrestha</t>
+        </is>
+      </c>
+      <c r="V65" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 09:48:35 PM</t>
+        </is>
+      </c>
+      <c r="W65" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 03:16:47 PM</t>
+        </is>
+      </c>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y65" s="3" t="inlineStr">
+        <is>
+          <t>27.67751</t>
+        </is>
+      </c>
+      <c r="Z65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA65" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB65" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC65" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD65" s="3" t="inlineStr"/>
+      <c r="AE65" s="3" t="inlineStr">
+        <is>
+          <t>Dhobighat, opposite of Union Hydropower LTD, , Lalitpur, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF65" s="3" t="inlineStr">
+        <is>
+          <t>mkshrestha004@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG65" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH65" s="3" t="inlineStr"/>
+      <c r="AI65" s="3" t="inlineStr"/>
+      <c r="AJ65" s="3" t="inlineStr"/>
+      <c r="AK65" s="3" t="inlineStr"/>
+      <c r="AL65" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM65" s="3" t="inlineStr">
+        <is>
+          <t>Yaman Bhandari</t>
+        </is>
+      </c>
+      <c r="AN65" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO65" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP65" s="3" t="inlineStr">
+        <is>
+          <t>85.30449</t>
+        </is>
+      </c>
+      <c r="AQ65" s="3" t="inlineStr"/>
+      <c r="AR65" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS65" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT65" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 28m</t>
+        </is>
+      </c>
+      <c r="AU65" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV65" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW65" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX65" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 3:10 PM</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV red light  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr"/>
+      <c r="K66" s="3" t="inlineStr"/>
+      <c r="L66" s="3" t="inlineStr"/>
+      <c r="M66" s="3" t="inlineStr"/>
+      <c r="N66" s="3" t="inlineStr"/>
+      <c r="O66" s="3" t="inlineStr"/>
+      <c r="P66" s="3" t="inlineStr"/>
+      <c r="Q66" s="3" t="inlineStr"/>
+      <c r="R66" s="3" t="inlineStr"/>
+      <c r="S66" s="3" t="inlineStr"/>
+      <c r="T66" s="3" t="inlineStr"/>
+      <c r="U66" s="3" t="inlineStr"/>
+      <c r="V66" s="3" t="inlineStr"/>
+      <c r="W66" s="3" t="inlineStr"/>
+      <c r="X66" s="3" t="inlineStr"/>
+      <c r="Y66" s="3" t="inlineStr"/>
+      <c r="Z66" s="3" t="inlineStr"/>
+      <c r="AA66" s="3" t="inlineStr"/>
+      <c r="AB66" s="3" t="inlineStr"/>
+      <c r="AC66" s="3" t="inlineStr"/>
+      <c r="AD66" s="3" t="inlineStr"/>
+      <c r="AE66" s="3" t="inlineStr"/>
+      <c r="AF66" s="3" t="inlineStr"/>
+      <c r="AG66" s="3" t="inlineStr"/>
+      <c r="AH66" s="3" t="inlineStr"/>
+      <c r="AI66" s="3" t="inlineStr"/>
+      <c r="AJ66" s="3" t="inlineStr"/>
+      <c r="AK66" s="3" t="inlineStr"/>
+      <c r="AL66" s="3" t="inlineStr"/>
+      <c r="AM66" s="3" t="inlineStr"/>
+      <c r="AN66" s="3" t="inlineStr"/>
+      <c r="AO66" s="3" t="inlineStr"/>
+      <c r="AP66" s="3" t="inlineStr"/>
+      <c r="AQ66" s="3" t="inlineStr"/>
+      <c r="AR66" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS66" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT66" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU66" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV66" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV red light  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW66" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX66" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -1171,7 +1171,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -13713,10 +13713,8 @@
           <t>Rojan Shrestha</t>
         </is>
       </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
-          <t>9841115011</t>
-        </is>
+      <c r="O64" s="3" t="n">
+        <v>9841115011</v>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
@@ -13751,10 +13749,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y64" s="3" t="inlineStr">
-        <is>
-          <t>27.69531</t>
-        </is>
+      <c r="Y64" s="3" t="n">
+        <v>27.69531</v>
       </c>
       <c r="Z64" s="3" t="inlineStr">
         <is>
@@ -13806,25 +13802,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN64" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN64" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
           <t>CDB387</t>
         </is>
       </c>
-      <c r="AP64" s="3" t="inlineStr">
-        <is>
-          <t>85.29619</t>
-        </is>
+      <c r="AP64" s="3" t="n">
+        <v>85.29619</v>
       </c>
       <c r="AQ64" s="3" t="inlineStr"/>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
@@ -13925,10 +13917,8 @@
           <t>Manan Shrestha</t>
         </is>
       </c>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
-          <t>9849517411</t>
-        </is>
+      <c r="O65" s="3" t="n">
+        <v>9849517411</v>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
@@ -13963,10 +13953,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y65" s="3" t="inlineStr">
-        <is>
-          <t>27.67751</t>
-        </is>
+      <c r="Y65" s="3" t="n">
+        <v>27.67751</v>
       </c>
       <c r="Z65" s="3" t="inlineStr">
         <is>
@@ -14018,25 +14006,21 @@
           <t>Yaman Bhandari</t>
         </is>
       </c>
-      <c r="AN65" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN65" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO65" s="3" t="inlineStr">
         <is>
           <t>3,5</t>
         </is>
       </c>
-      <c r="AP65" s="3" t="inlineStr">
-        <is>
-          <t>85.30449</t>
-        </is>
+      <c r="AP65" s="3" t="n">
+        <v>85.30449</v>
       </c>
       <c r="AQ65" s="3" t="inlineStr"/>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>92.3%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>62.9%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.1%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>11.4%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -850,7 +850,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>7</v>
@@ -859,7 +859,7 @@
         <v>5</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -893,26 +893,26 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>2</v>
@@ -921,20 +921,20 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -943,17 +943,17 @@
         <v>0</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>General Query &amp; Feedback</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -977,11 +977,11 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1061,7 +1061,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1074,44 +1074,100 @@
         <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="F11" s="4" t="n">
+      <c r="D13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>52</v>
+      <c r="G13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1125,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX66"/>
+  <dimension ref="A1:AX71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1155,7 +1211,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="34" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="21" customWidth="1" min="28" max="28"/>
+    <col width="28" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
@@ -1171,7 +1227,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -14162,6 +14218,1078 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 3:18 PM</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Case : Red light in stb  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>Red light in stb</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344044</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Tolangi</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Tolangi</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>9860562935</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr"/>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 03:36:15 PM</t>
+        </is>
+      </c>
+      <c r="S67" s="3" t="inlineStr"/>
+      <c r="T67" s="3" t="inlineStr"/>
+      <c r="U67" s="3" t="inlineStr">
+        <is>
+          <t>9860562935</t>
+        </is>
+      </c>
+      <c r="V67" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 05:22:11 PM</t>
+        </is>
+      </c>
+      <c r="W67" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 03:36:15 PM</t>
+        </is>
+      </c>
+      <c r="X67" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y67" s="3" t="inlineStr">
+        <is>
+          <t>27.67783</t>
+        </is>
+      </c>
+      <c r="Z67" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA67" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB67" s="3" t="inlineStr">
+        <is>
+          <t>customer experience sales</t>
+        </is>
+      </c>
+      <c r="AC67" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD67" s="3" t="inlineStr"/>
+      <c r="AE67" s="3" t="inlineStr">
+        <is>
+          <t>Dhobigha New Road, Manakamana Mandir, Next To Sugam Gas Depo, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF67" s="3" t="inlineStr">
+        <is>
+          <t>st.sunu35@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG67" s="3" t="inlineStr">
+        <is>
+          <t>Replace SKYCOM to NETTV</t>
+        </is>
+      </c>
+      <c r="AH67" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI67" s="3" t="inlineStr"/>
+      <c r="AJ67" s="3" t="inlineStr"/>
+      <c r="AK67" s="3" t="inlineStr"/>
+      <c r="AL67" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM67" s="3" t="inlineStr">
+        <is>
+          <t>Rabindra Bohora</t>
+        </is>
+      </c>
+      <c r="AN67" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO67" s="3" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="AP67" s="3" t="inlineStr">
+        <is>
+          <t>85.305829</t>
+        </is>
+      </c>
+      <c r="AQ67" s="3" t="inlineStr"/>
+      <c r="AR67" s="3" t="inlineStr">
+        <is>
+          <t>Case : Red light in stb  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS67" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT67" s="3" t="inlineStr">
+        <is>
+          <t>2d 22h 14m</t>
+        </is>
+      </c>
+      <c r="AU67" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV67" s="3" t="inlineStr">
+        <is>
+          <t>Case : Red light in stb  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW67" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX67" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 3:40 PM</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN SET UP BOX   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>NO LIGHT IN SET UP BOX</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345881</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>Guna Raj Khatri</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>Guna Raj Khatri</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>9843419078</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="inlineStr"/>
+      <c r="R68" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 03:40:02 PM</t>
+        </is>
+      </c>
+      <c r="S68" s="3" t="inlineStr"/>
+      <c r="T68" s="3" t="inlineStr"/>
+      <c r="U68" s="3" t="inlineStr">
+        <is>
+          <t>9843419078</t>
+        </is>
+      </c>
+      <c r="V68" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 11:25:20 AM</t>
+        </is>
+      </c>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 03:40:02 PM</t>
+        </is>
+      </c>
+      <c r="X68" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y68" s="3" t="inlineStr">
+        <is>
+          <t>27.74193</t>
+        </is>
+      </c>
+      <c r="Z68" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA68" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB68" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC68" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD68" s="3" t="inlineStr"/>
+      <c r="AE68" s="3" t="inlineStr">
+        <is>
+          <t>40m from Minar High School,Basundhara,Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF68" s="3" t="inlineStr">
+        <is>
+          <t>gunarajkhatri123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG68" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH68" s="3" t="inlineStr"/>
+      <c r="AI68" s="3" t="inlineStr">
+        <is>
+          <t>14:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ68" s="3" t="inlineStr"/>
+      <c r="AK68" s="3" t="inlineStr"/>
+      <c r="AL68" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM68" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN68" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO68" s="3" t="inlineStr">
+        <is>
+          <t>L9-8</t>
+        </is>
+      </c>
+      <c r="AP68" s="3" t="inlineStr">
+        <is>
+          <t>85.33546</t>
+        </is>
+      </c>
+      <c r="AQ68" s="3" t="inlineStr"/>
+      <c r="AR68" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN SET UP BOX   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS68" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT68" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 14m</t>
+        </is>
+      </c>
+      <c r="AU68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV68" s="3" t="inlineStr">
+        <is>
+          <t>Case : NO LIGHT IN SET UP BOX   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX68" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 3:33 PM</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344230</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>Barsha Gurung</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>Barsha Gurung</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>9845510104</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr"/>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 03:33:26 PM</t>
+        </is>
+      </c>
+      <c r="S69" s="3" t="inlineStr"/>
+      <c r="T69" s="3" t="inlineStr"/>
+      <c r="U69" s="3" t="inlineStr">
+        <is>
+          <t>9851323196</t>
+        </is>
+      </c>
+      <c r="V69" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 08:28:00 PM</t>
+        </is>
+      </c>
+      <c r="W69" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 03:33:26 PM</t>
+        </is>
+      </c>
+      <c r="X69" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y69" s="3" t="inlineStr"/>
+      <c r="Z69" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA69" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB69" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC69" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD69" s="3" t="inlineStr"/>
+      <c r="AE69" s="3" t="inlineStr">
+        <is>
+          <t>near by White Mountain School - Government school - Kathmandu Metropolitan, Kathmandu, Bagmati, Cent</t>
+        </is>
+      </c>
+      <c r="AF69" s="3" t="inlineStr">
+        <is>
+          <t>binodgurung212@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG69" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH69" s="3" t="inlineStr"/>
+      <c r="AI69" s="3" t="inlineStr">
+        <is>
+          <t>01:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ69" s="3" t="inlineStr"/>
+      <c r="AK69" s="3" t="inlineStr"/>
+      <c r="AL69" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM69" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN69" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO69" s="3" t="inlineStr">
+        <is>
+          <t>L7-3</t>
+        </is>
+      </c>
+      <c r="AP69" s="3" t="inlineStr"/>
+      <c r="AQ69" s="3" t="inlineStr"/>
+      <c r="AR69" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS69" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT69" s="3" t="inlineStr">
+        <is>
+          <t>2d 19h 5m</t>
+        </is>
+      </c>
+      <c r="AU69" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV69" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW69" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX69" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 3:24 PM</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv adaptor issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>iptv adaptor issue</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345193</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>Bimala Thapa</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>Bimala Thapa</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>9861032606</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="inlineStr"/>
+      <c r="R70" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 06:32:07 PM</t>
+        </is>
+      </c>
+      <c r="S70" s="3" t="inlineStr"/>
+      <c r="T70" s="3" t="inlineStr"/>
+      <c r="U70" s="3" t="inlineStr">
+        <is>
+          <t>9861032606</t>
+        </is>
+      </c>
+      <c r="V70" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 06:18:40 PM</t>
+        </is>
+      </c>
+      <c r="W70" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 03:24:04 PM</t>
+        </is>
+      </c>
+      <c r="X70" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y70" s="3" t="inlineStr">
+        <is>
+          <t>27.682479</t>
+        </is>
+      </c>
+      <c r="Z70" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA70" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB70" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC70" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD70" s="3" t="inlineStr"/>
+      <c r="AE70" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri ,Naikap ward no:15,panchakanya marga,near Munal Chowk Club, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF70" s="3" t="inlineStr">
+        <is>
+          <t>prabeshroka90@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG70" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH70" s="3" t="inlineStr"/>
+      <c r="AI70" s="3" t="inlineStr">
+        <is>
+          <t>17:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ70" s="3" t="inlineStr"/>
+      <c r="AK70" s="3" t="inlineStr"/>
+      <c r="AL70" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM70" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN70" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO70" s="3" t="inlineStr">
+        <is>
+          <t>CDB568</t>
+        </is>
+      </c>
+      <c r="AP70" s="3" t="inlineStr">
+        <is>
+          <t>85.266186</t>
+        </is>
+      </c>
+      <c r="AQ70" s="3" t="inlineStr"/>
+      <c r="AR70" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv adaptor issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS70" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 51m</t>
+        </is>
+      </c>
+      <c r="AT70" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 5m</t>
+        </is>
+      </c>
+      <c r="AU70" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV70" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv adaptor issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW70" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX70" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 3:23 PM</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv adaptor issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>iptv adaptor issue</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345193</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>Bimala Thapa</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>Bimala Thapa</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>9861032606</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr"/>
+      <c r="R71" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 06:32:07 PM</t>
+        </is>
+      </c>
+      <c r="S71" s="3" t="inlineStr"/>
+      <c r="T71" s="3" t="inlineStr"/>
+      <c r="U71" s="3" t="inlineStr">
+        <is>
+          <t>9861032606</t>
+        </is>
+      </c>
+      <c r="V71" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 06:18:40 PM</t>
+        </is>
+      </c>
+      <c r="W71" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 03:24:04 PM</t>
+        </is>
+      </c>
+      <c r="X71" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y71" s="3" t="inlineStr">
+        <is>
+          <t>27.682479</t>
+        </is>
+      </c>
+      <c r="Z71" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA71" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB71" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC71" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD71" s="3" t="inlineStr"/>
+      <c r="AE71" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri ,Naikap ward no:15,panchakanya marga,near Munal Chowk Club, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF71" s="3" t="inlineStr">
+        <is>
+          <t>prabeshroka90@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG71" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH71" s="3" t="inlineStr"/>
+      <c r="AI71" s="3" t="inlineStr">
+        <is>
+          <t>17:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ71" s="3" t="inlineStr"/>
+      <c r="AK71" s="3" t="inlineStr"/>
+      <c r="AL71" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM71" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN71" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO71" s="3" t="inlineStr">
+        <is>
+          <t>CDB568</t>
+        </is>
+      </c>
+      <c r="AP71" s="3" t="inlineStr">
+        <is>
+          <t>85.266186</t>
+        </is>
+      </c>
+      <c r="AQ71" s="3" t="inlineStr"/>
+      <c r="AR71" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv adaptor issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS71" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 51m</t>
+        </is>
+      </c>
+      <c r="AT71" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 5m</t>
+        </is>
+      </c>
+      <c r="AU71" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV71" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv adaptor issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW71" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX71" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.9%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.7%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>25.3%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>12.0%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>7</v>
@@ -856,10 +856,10 @@
         <v>7</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>3</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>10</v>
@@ -1164,10 +1164,10 @@
         <v>7</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1181,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX71"/>
+  <dimension ref="A1:AX76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14285,10 +14285,8 @@
           <t>Sunita Tolangi</t>
         </is>
       </c>
-      <c r="O67" s="3" t="inlineStr">
-        <is>
-          <t>9860562935</t>
-        </is>
+      <c r="O67" s="3" t="n">
+        <v>9860562935</v>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
@@ -14323,10 +14321,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y67" s="3" t="inlineStr">
-        <is>
-          <t>27.67783</t>
-        </is>
+      <c r="Y67" s="3" t="n">
+        <v>27.67783</v>
       </c>
       <c r="Z67" s="3" t="inlineStr">
         <is>
@@ -14364,10 +14360,8 @@
           <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
-      <c r="AH67" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH67" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI67" s="3" t="inlineStr"/>
       <c r="AJ67" s="3" t="inlineStr"/>
@@ -14382,25 +14376,21 @@
           <t>Rabindra Bohora</t>
         </is>
       </c>
-      <c r="AN67" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN67" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO67" s="3" t="inlineStr">
         <is>
           <t>2,3</t>
         </is>
       </c>
-      <c r="AP67" s="3" t="inlineStr">
-        <is>
-          <t>85.305829</t>
-        </is>
+      <c r="AP67" s="3" t="n">
+        <v>85.305829</v>
       </c>
       <c r="AQ67" s="3" t="inlineStr"/>
       <c r="AR67" s="3" t="inlineStr">
         <is>
-          <t>Case : Red light in stb  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS67" s="3" t="inlineStr">
@@ -14501,10 +14491,8 @@
           <t>Guna Raj Khatri</t>
         </is>
       </c>
-      <c r="O68" s="3" t="inlineStr">
-        <is>
-          <t>9843419078</t>
-        </is>
+      <c r="O68" s="3" t="n">
+        <v>9843419078</v>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
@@ -14539,10 +14527,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y68" s="3" t="inlineStr">
-        <is>
-          <t>27.74193</t>
-        </is>
+      <c r="Y68" s="3" t="n">
+        <v>27.74193</v>
       </c>
       <c r="Z68" s="3" t="inlineStr">
         <is>
@@ -14598,25 +14584,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN68" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN68" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO68" s="3" t="inlineStr">
         <is>
           <t>L9-8</t>
         </is>
       </c>
-      <c r="AP68" s="3" t="inlineStr">
-        <is>
-          <t>85.33546</t>
-        </is>
+      <c r="AP68" s="3" t="n">
+        <v>85.33546</v>
       </c>
       <c r="AQ68" s="3" t="inlineStr"/>
       <c r="AR68" s="3" t="inlineStr">
         <is>
-          <t>Case : NO LIGHT IN SET UP BOX   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS68" s="3" t="inlineStr">
@@ -14717,10 +14699,8 @@
           <t>Barsha Gurung</t>
         </is>
       </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
-          <t>9845510104</t>
-        </is>
+      <c r="O69" s="3" t="n">
+        <v>9845510104</v>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
@@ -14810,10 +14790,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN69" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN69" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO69" s="3" t="inlineStr">
         <is>
@@ -14824,7 +14802,7 @@
       <c r="AQ69" s="3" t="inlineStr"/>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
@@ -14925,10 +14903,8 @@
           <t>Bimala Thapa</t>
         </is>
       </c>
-      <c r="O70" s="3" t="inlineStr">
-        <is>
-          <t>9861032606</t>
-        </is>
+      <c r="O70" s="3" t="n">
+        <v>9861032606</v>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
@@ -14963,10 +14939,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y70" s="3" t="inlineStr">
-        <is>
-          <t>27.682479</t>
-        </is>
+      <c r="Y70" s="3" t="n">
+        <v>27.682479</v>
       </c>
       <c r="Z70" s="3" t="inlineStr">
         <is>
@@ -15022,25 +14996,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN70" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN70" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO70" s="3" t="inlineStr">
         <is>
           <t>CDB568</t>
         </is>
       </c>
-      <c r="AP70" s="3" t="inlineStr">
-        <is>
-          <t>85.266186</t>
-        </is>
+      <c r="AP70" s="3" t="n">
+        <v>85.266186</v>
       </c>
       <c r="AQ70" s="3" t="inlineStr"/>
       <c r="AR70" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv adaptor issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS70" s="3" t="inlineStr">
@@ -15141,10 +15111,8 @@
           <t>Bimala Thapa</t>
         </is>
       </c>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
-          <t>9861032606</t>
-        </is>
+      <c r="O71" s="3" t="n">
+        <v>9861032606</v>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
@@ -15179,10 +15147,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y71" s="3" t="inlineStr">
-        <is>
-          <t>27.682479</t>
-        </is>
+      <c r="Y71" s="3" t="n">
+        <v>27.682479</v>
       </c>
       <c r="Z71" s="3" t="inlineStr">
         <is>
@@ -15238,55 +15204,1115 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN71" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN71" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO71" s="3" t="inlineStr">
         <is>
           <t>CDB568</t>
         </is>
       </c>
-      <c r="AP71" s="3" t="inlineStr">
-        <is>
-          <t>85.266186</t>
-        </is>
+      <c r="AP71" s="3" t="n">
+        <v>85.266186</v>
       </c>
       <c r="AQ71" s="3" t="inlineStr"/>
       <c r="AR71" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS71" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 51m</t>
+        </is>
+      </c>
+      <c r="AT71" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 5m</t>
+        </is>
+      </c>
+      <c r="AU71" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV71" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv adaptor issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS71" s="3" t="inlineStr">
-        <is>
-          <t>1d 20h 51m</t>
-        </is>
-      </c>
-      <c r="AT71" s="3" t="inlineStr">
-        <is>
-          <t>1d 21h 5m</t>
-        </is>
-      </c>
-      <c r="AU71" s="3" t="inlineStr">
+      <c r="AW71" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX71" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 4:01 PM</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345900</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>Pramil Luitel</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>Pramil Luitel</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>9841082626</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q72" s="3" t="inlineStr"/>
+      <c r="R72" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 11:35:49 AM</t>
+        </is>
+      </c>
+      <c r="S72" s="3" t="inlineStr"/>
+      <c r="T72" s="3" t="inlineStr"/>
+      <c r="U72" s="3" t="inlineStr">
+        <is>
+          <t>9841082626</t>
+        </is>
+      </c>
+      <c r="V72" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 11:35:49 AM</t>
+        </is>
+      </c>
+      <c r="W72" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 04:01:41 PM</t>
+        </is>
+      </c>
+      <c r="X72" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y72" s="3" t="inlineStr">
+        <is>
+          <t>27.68994</t>
+        </is>
+      </c>
+      <c r="Z72" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA72" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB72" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC72" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD72" s="3" t="inlineStr"/>
+      <c r="AE72" s="3" t="inlineStr">
+        <is>
+          <t>Satungal BAHYAGAU NAIKAP, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF72" s="3" t="inlineStr">
+        <is>
+          <t>luitelpramila03@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG72" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH72" s="3" t="inlineStr"/>
+      <c r="AI72" s="3" t="inlineStr">
+        <is>
+          <t>14:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ72" s="3" t="inlineStr"/>
+      <c r="AK72" s="3" t="inlineStr"/>
+      <c r="AL72" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM72" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN72" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO72" s="3" t="inlineStr">
+        <is>
+          <t>3,9</t>
+        </is>
+      </c>
+      <c r="AP72" s="3" t="inlineStr">
+        <is>
+          <t>85.26628</t>
+        </is>
+      </c>
+      <c r="AQ72" s="3" t="inlineStr"/>
+      <c r="AR72" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS72" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 25m</t>
+        </is>
+      </c>
+      <c r="AT72" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 25m</t>
+        </is>
+      </c>
+      <c r="AU72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV72" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW72" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX72" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 3:58 PM</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343458</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>Nigam Bakhariya</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>Nigam Bakhariya</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>9869216939</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="inlineStr"/>
+      <c r="R73" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:29:33 AM</t>
+        </is>
+      </c>
+      <c r="S73" s="3" t="inlineStr"/>
+      <c r="T73" s="3" t="inlineStr"/>
+      <c r="U73" s="3" t="inlineStr">
+        <is>
+          <t>9869216939</t>
+        </is>
+      </c>
+      <c r="V73" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 10:29:33 AM</t>
+        </is>
+      </c>
+      <c r="W73" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 03:58:28 PM</t>
+        </is>
+      </c>
+      <c r="X73" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y73" s="3" t="inlineStr"/>
+      <c r="Z73" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA73" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB73" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC73" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD73" s="3" t="inlineStr"/>
+      <c r="AE73" s="3" t="inlineStr">
+        <is>
+          <t>M7CH+6J8 Kirtipur 44600,NEAR Panga Bus Park, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF73" s="3" t="inlineStr">
+        <is>
+          <t>nigambakhariya123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG73" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH73" s="3" t="inlineStr"/>
+      <c r="AI73" s="3" t="inlineStr">
+        <is>
+          <t>11:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ73" s="3" t="inlineStr"/>
+      <c r="AK73" s="3" t="inlineStr"/>
+      <c r="AL73" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM73" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN73" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO73" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP73" s="3" t="inlineStr"/>
+      <c r="AQ73" s="3" t="inlineStr"/>
+      <c r="AR73" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS73" s="3" t="inlineStr">
+        <is>
+          <t>3d 5h 28m</t>
+        </is>
+      </c>
+      <c r="AT73" s="3" t="inlineStr">
+        <is>
+          <t>3d 5h 28m</t>
+        </is>
+      </c>
+      <c r="AU73" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV71" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv adaptor issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW71" s="3" t="inlineStr">
+      <c r="AV73" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW73" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX73" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 4:00 PM</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346370</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>Kumari Nanda Jaiswar Bhatta</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>Kumari Nanda Jaiswar Bhatta</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>9818548099</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q74" s="3" t="inlineStr"/>
+      <c r="R74" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 04:00:56 PM</t>
+        </is>
+      </c>
+      <c r="S74" s="3" t="inlineStr"/>
+      <c r="T74" s="3" t="inlineStr"/>
+      <c r="U74" s="3" t="inlineStr">
+        <is>
+          <t>9867369591</t>
+        </is>
+      </c>
+      <c r="V74" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:48:50 PM</t>
+        </is>
+      </c>
+      <c r="W74" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 04:00:56 PM</t>
+        </is>
+      </c>
+      <c r="X74" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y74" s="3" t="inlineStr">
+        <is>
+          <t>27.68548</t>
+        </is>
+      </c>
+      <c r="Z74" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA74" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB74" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC74" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD74" s="3" t="inlineStr"/>
+      <c r="AE74" s="3" t="inlineStr">
+        <is>
+          <t>Madhya Marg, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF74" s="3" t="inlineStr">
+        <is>
+          <t>anshusafalpatel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG74" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH74" s="3" t="inlineStr"/>
+      <c r="AI74" s="3" t="inlineStr"/>
+      <c r="AJ74" s="3" t="inlineStr"/>
+      <c r="AK74" s="3" t="inlineStr"/>
+      <c r="AL74" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM74" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN74" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO74" s="3" t="inlineStr">
+        <is>
+          <t>CDB488</t>
+        </is>
+      </c>
+      <c r="AP74" s="3" t="inlineStr">
+        <is>
+          <t>85.33084</t>
+        </is>
+      </c>
+      <c r="AQ74" s="3" t="inlineStr"/>
+      <c r="AR74" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS74" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT74" s="3" t="inlineStr">
+        <is>
+          <t>23h 12m</t>
+        </is>
+      </c>
+      <c r="AU74" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV74" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW74" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX74" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 3:57 PM</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346049</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>Jagadish Dhami</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
+          <t>Jagadish Dhami</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>9865964576</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q75" s="3" t="inlineStr"/>
+      <c r="R75" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 03:57:56 PM</t>
+        </is>
+      </c>
+      <c r="S75" s="3" t="inlineStr"/>
+      <c r="T75" s="3" t="inlineStr"/>
+      <c r="U75" s="3" t="inlineStr">
+        <is>
+          <t>9865964576</t>
+        </is>
+      </c>
+      <c r="V75" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 01:17:54 PM</t>
+        </is>
+      </c>
+      <c r="W75" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 03:57:56 PM</t>
+        </is>
+      </c>
+      <c r="X75" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y75" s="3" t="inlineStr">
+        <is>
+          <t>27.684093</t>
+        </is>
+      </c>
+      <c r="Z75" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA75" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB75" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC75" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD75" s="3" t="inlineStr"/>
+      <c r="AE75" s="3" t="inlineStr">
+        <is>
+          <t>Buddhanagar Near  Shandar Mo:Mo, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF75" s="3" t="inlineStr">
+        <is>
+          <t>jadgishdhami@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG75" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH75" s="3" t="inlineStr"/>
+      <c r="AI75" s="3" t="inlineStr">
+        <is>
+          <t>12:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ75" s="3" t="inlineStr"/>
+      <c r="AK75" s="3" t="inlineStr"/>
+      <c r="AL75" s="3" t="inlineStr">
+        <is>
+          <t>Sitaram Adhikari</t>
+        </is>
+      </c>
+      <c r="AM75" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN75" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO75" s="3" t="inlineStr">
+        <is>
+          <t>CDB077</t>
+        </is>
+      </c>
+      <c r="AP75" s="3" t="inlineStr">
+        <is>
+          <t>85.332165</t>
+        </is>
+      </c>
+      <c r="AQ75" s="3" t="inlineStr"/>
+      <c r="AR75" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS75" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT75" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 40m</t>
+        </is>
+      </c>
+      <c r="AU75" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV75" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW75" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
         </is>
       </c>
-      <c r="AX71" s="3" t="inlineStr">
-        <is>
-          <t>Sunil Chaudhary</t>
+      <c r="AX75" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 3:54 PM</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346142</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>Jewellery Palace Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>Jewellery Palace Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
+          <t>9801028000</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q76" s="3" t="inlineStr"/>
+      <c r="R76" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 02:21:37 PM</t>
+        </is>
+      </c>
+      <c r="S76" s="3" t="inlineStr"/>
+      <c r="T76" s="3" t="inlineStr"/>
+      <c r="U76" s="3" t="inlineStr">
+        <is>
+          <t>9801028000</t>
+        </is>
+      </c>
+      <c r="V76" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 02:21:37 PM</t>
+        </is>
+      </c>
+      <c r="W76" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 03:54:42 PM</t>
+        </is>
+      </c>
+      <c r="X76" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y76" s="3" t="inlineStr">
+        <is>
+          <t>27.7049</t>
+        </is>
+      </c>
+      <c r="Z76" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA76" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB76" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC76" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD76" s="3" t="inlineStr"/>
+      <c r="AE76" s="3" t="inlineStr">
+        <is>
+          <t>Near Healthy Living Nepal pvt. Ltd. Gaushala, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF76" s="3" t="inlineStr">
+        <is>
+          <t>Alankarjain102@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG76" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH76" s="3" t="inlineStr"/>
+      <c r="AI76" s="3" t="inlineStr"/>
+      <c r="AJ76" s="3" t="inlineStr"/>
+      <c r="AK76" s="3" t="inlineStr"/>
+      <c r="AL76" s="3" t="inlineStr">
+        <is>
+          <t>Sabina Baskota</t>
+        </is>
+      </c>
+      <c r="AM76" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN76" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO76" s="3" t="inlineStr">
+        <is>
+          <t>L11-7</t>
+        </is>
+      </c>
+      <c r="AP76" s="3" t="inlineStr">
+        <is>
+          <t>85.33648</t>
+        </is>
+      </c>
+      <c r="AQ76" s="3" t="inlineStr"/>
+      <c r="AR76" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS76" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 33m</t>
+        </is>
+      </c>
+      <c r="AT76" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 33m</t>
+        </is>
+      </c>
+      <c r="AU76" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV76" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW76" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX76" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>93.3%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>64.1%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.6%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.1%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -850,7 +850,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>7</v>
@@ -859,7 +859,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -893,26 +893,26 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>2</v>
@@ -921,26 +921,26 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>2</v>
@@ -1033,7 +1033,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1071,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -1089,7 +1089,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -1143,31 +1143,59 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F13" s="4" t="n">
+      <c r="D14" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F14" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="H13" s="4" t="n">
-        <v>60</v>
+      <c r="H14" s="4" t="n">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1181,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX76"/>
+  <dimension ref="A1:AX79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1215,7 +1243,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="31" customWidth="1" min="32" max="32"/>
+    <col width="34" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -15319,10 +15347,8 @@
           <t>Pramil Luitel</t>
         </is>
       </c>
-      <c r="O72" s="3" t="inlineStr">
-        <is>
-          <t>9841082626</t>
-        </is>
+      <c r="O72" s="3" t="n">
+        <v>9841082626</v>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
@@ -15357,10 +15383,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y72" s="3" t="inlineStr">
-        <is>
-          <t>27.68994</t>
-        </is>
+      <c r="Y72" s="3" t="n">
+        <v>27.68994</v>
       </c>
       <c r="Z72" s="3" t="inlineStr">
         <is>
@@ -15416,25 +15440,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN72" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN72" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO72" s="3" t="inlineStr">
         <is>
           <t>3,9</t>
         </is>
       </c>
-      <c r="AP72" s="3" t="inlineStr">
-        <is>
-          <t>85.26628</t>
-        </is>
+      <c r="AP72" s="3" t="n">
+        <v>85.26627999999999</v>
       </c>
       <c r="AQ72" s="3" t="inlineStr"/>
       <c r="AR72" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS72" s="3" t="inlineStr">
@@ -15535,10 +15555,8 @@
           <t>Nigam Bakhariya</t>
         </is>
       </c>
-      <c r="O73" s="3" t="inlineStr">
-        <is>
-          <t>9869216939</t>
-        </is>
+      <c r="O73" s="3" t="n">
+        <v>9869216939</v>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
@@ -15628,10 +15646,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN73" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN73" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO73" s="3" t="inlineStr">
         <is>
@@ -15642,7 +15658,7 @@
       <c r="AQ73" s="3" t="inlineStr"/>
       <c r="AR73" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS73" s="3" t="inlineStr">
@@ -15743,10 +15759,8 @@
           <t>Kumari Nanda Jaiswar Bhatta</t>
         </is>
       </c>
-      <c r="O74" s="3" t="inlineStr">
-        <is>
-          <t>9818548099</t>
-        </is>
+      <c r="O74" s="3" t="n">
+        <v>9818548099</v>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
@@ -15781,10 +15795,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y74" s="3" t="inlineStr">
-        <is>
-          <t>27.68548</t>
-        </is>
+      <c r="Y74" s="3" t="n">
+        <v>27.68548</v>
       </c>
       <c r="Z74" s="3" t="inlineStr">
         <is>
@@ -15836,25 +15848,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN74" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN74" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO74" s="3" t="inlineStr">
         <is>
           <t>CDB488</t>
         </is>
       </c>
-      <c r="AP74" s="3" t="inlineStr">
-        <is>
-          <t>85.33084</t>
-        </is>
+      <c r="AP74" s="3" t="n">
+        <v>85.33083999999999</v>
       </c>
       <c r="AQ74" s="3" t="inlineStr"/>
       <c r="AR74" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS74" s="3" t="inlineStr">
@@ -15955,10 +15963,8 @@
           <t>Jagadish Dhami</t>
         </is>
       </c>
-      <c r="O75" s="3" t="inlineStr">
-        <is>
-          <t>9865964576</t>
-        </is>
+      <c r="O75" s="3" t="n">
+        <v>9865964576</v>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
@@ -15993,10 +15999,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y75" s="3" t="inlineStr">
-        <is>
-          <t>27.684093</t>
-        </is>
+      <c r="Y75" s="3" t="n">
+        <v>27.684093</v>
       </c>
       <c r="Z75" s="3" t="inlineStr">
         <is>
@@ -16052,25 +16056,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN75" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN75" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO75" s="3" t="inlineStr">
         <is>
           <t>CDB077</t>
         </is>
       </c>
-      <c r="AP75" s="3" t="inlineStr">
-        <is>
-          <t>85.332165</t>
-        </is>
+      <c r="AP75" s="3" t="n">
+        <v>85.332165</v>
       </c>
       <c r="AQ75" s="3" t="inlineStr"/>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">
@@ -16171,10 +16171,8 @@
           <t>Jewellery Palace Pvt Ltd</t>
         </is>
       </c>
-      <c r="O76" s="3" t="inlineStr">
-        <is>
-          <t>9801028000</t>
-        </is>
+      <c r="O76" s="3" t="n">
+        <v>9801028000</v>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
@@ -16209,10 +16207,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y76" s="3" t="inlineStr">
-        <is>
-          <t>27.7049</t>
-        </is>
+      <c r="Y76" s="3" t="n">
+        <v>27.7049</v>
       </c>
       <c r="Z76" s="3" t="inlineStr">
         <is>
@@ -16264,47 +16260,43 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN76" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN76" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO76" s="3" t="inlineStr">
         <is>
           <t>L11-7</t>
         </is>
       </c>
-      <c r="AP76" s="3" t="inlineStr">
-        <is>
-          <t>85.33648</t>
-        </is>
+      <c r="AP76" s="3" t="n">
+        <v>85.33647999999999</v>
       </c>
       <c r="AQ76" s="3" t="inlineStr"/>
       <c r="AR76" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS76" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 33m</t>
+        </is>
+      </c>
+      <c r="AT76" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 33m</t>
+        </is>
+      </c>
+      <c r="AU76" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV76" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS76" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 33m</t>
-        </is>
-      </c>
-      <c r="AT76" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 33m</t>
-        </is>
-      </c>
-      <c r="AU76" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV76" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router upgrade  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW76" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -16313,6 +16305,646 @@
       <c r="AX76" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 4:13 PM</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344387</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>Structen Construction Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
+          <t>Structen Construction Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>9803810701</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q77" s="3" t="inlineStr"/>
+      <c r="R77" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 04:13:34 PM</t>
+        </is>
+      </c>
+      <c r="S77" s="3" t="inlineStr"/>
+      <c r="T77" s="3" t="inlineStr"/>
+      <c r="U77" s="3" t="inlineStr">
+        <is>
+          <t>9803810701</t>
+        </is>
+      </c>
+      <c r="V77" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 07:10:04 AM</t>
+        </is>
+      </c>
+      <c r="W77" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 04:13:34 PM</t>
+        </is>
+      </c>
+      <c r="X77" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y77" s="3" t="inlineStr"/>
+      <c r="Z77" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA77" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB77" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC77" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD77" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE77" s="3" t="inlineStr">
+        <is>
+          <t>Nakhu Near Siddhivinayak Ganeshthan, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF77" s="3" t="inlineStr">
+        <is>
+          <t>construction.structen@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG77" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH77" s="3" t="inlineStr"/>
+      <c r="AI77" s="3" t="inlineStr">
+        <is>
+          <t>02:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ77" s="3" t="inlineStr"/>
+      <c r="AK77" s="3" t="inlineStr"/>
+      <c r="AL77" s="3" t="inlineStr"/>
+      <c r="AM77" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN77" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO77" s="3" t="inlineStr">
+        <is>
+          <t>2,11</t>
+        </is>
+      </c>
+      <c r="AP77" s="3" t="inlineStr"/>
+      <c r="AQ77" s="3" t="inlineStr"/>
+      <c r="AR77" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS77" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT77" s="3" t="inlineStr">
+        <is>
+          <t>2d 9h 3m</t>
+        </is>
+      </c>
+      <c r="AU77" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV77" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW77" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX77" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 4:02 PM</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr"/>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345900</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>Pramil Luitel</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>Pramil Luitel</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="inlineStr">
+        <is>
+          <t>9841082626</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q78" s="3" t="inlineStr"/>
+      <c r="R78" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 11:35:49 AM</t>
+        </is>
+      </c>
+      <c r="S78" s="3" t="inlineStr"/>
+      <c r="T78" s="3" t="inlineStr"/>
+      <c r="U78" s="3" t="inlineStr">
+        <is>
+          <t>9841082626</t>
+        </is>
+      </c>
+      <c r="V78" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 11:35:49 AM</t>
+        </is>
+      </c>
+      <c r="W78" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 04:02:07 PM</t>
+        </is>
+      </c>
+      <c r="X78" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y78" s="3" t="inlineStr">
+        <is>
+          <t>27.68994</t>
+        </is>
+      </c>
+      <c r="Z78" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA78" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB78" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC78" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD78" s="3" t="inlineStr"/>
+      <c r="AE78" s="3" t="inlineStr">
+        <is>
+          <t>Satungal BAHYAGAU NAIKAP, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF78" s="3" t="inlineStr">
+        <is>
+          <t>luitelpramila03@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG78" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH78" s="3" t="inlineStr"/>
+      <c r="AI78" s="3" t="inlineStr">
+        <is>
+          <t>14:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ78" s="3" t="inlineStr"/>
+      <c r="AK78" s="3" t="inlineStr"/>
+      <c r="AL78" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM78" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN78" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO78" s="3" t="inlineStr">
+        <is>
+          <t>3,9</t>
+        </is>
+      </c>
+      <c r="AP78" s="3" t="inlineStr">
+        <is>
+          <t>85.26628</t>
+        </is>
+      </c>
+      <c r="AQ78" s="3" t="inlineStr"/>
+      <c r="AR78" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS78" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 26m</t>
+        </is>
+      </c>
+      <c r="AT78" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 26m</t>
+        </is>
+      </c>
+      <c r="AU78" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV78" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW78" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX78" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 4:02 PM</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347381</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>Bedhari Chaulagain</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
+          <t>Bedhari Chaulagain</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>9841121967</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q79" s="3" t="inlineStr"/>
+      <c r="R79" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 04:02:00 PM</t>
+        </is>
+      </c>
+      <c r="S79" s="3" t="inlineStr"/>
+      <c r="T79" s="3" t="inlineStr"/>
+      <c r="U79" s="3" t="inlineStr">
+        <is>
+          <t>9841121967</t>
+        </is>
+      </c>
+      <c r="V79" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 02:57:55 PM</t>
+        </is>
+      </c>
+      <c r="W79" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 04:02:00 PM</t>
+        </is>
+      </c>
+      <c r="X79" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y79" s="3" t="inlineStr">
+        <is>
+          <t>27.71799</t>
+        </is>
+      </c>
+      <c r="Z79" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA79" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB79" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC79" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD79" s="3" t="inlineStr"/>
+      <c r="AE79" s="3" t="inlineStr">
+        <is>
+          <t>27.718545021852147, 85.3536778372342, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF79" s="3" t="inlineStr">
+        <is>
+          <t>chaulagaintara95@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG79" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH79" s="3" t="inlineStr"/>
+      <c r="AI79" s="3" t="inlineStr">
+        <is>
+          <t>01:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ79" s="3" t="inlineStr"/>
+      <c r="AK79" s="3" t="inlineStr"/>
+      <c r="AL79" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM79" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN79" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO79" s="3" t="inlineStr">
+        <is>
+          <t>L2-8</t>
+        </is>
+      </c>
+      <c r="AP79" s="3" t="inlineStr">
+        <is>
+          <t>85.35404</t>
+        </is>
+      </c>
+      <c r="AQ79" s="3" t="inlineStr"/>
+      <c r="AR79" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS79" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT79" s="3" t="inlineStr">
+        <is>
+          <t>1h 4m</t>
+        </is>
+      </c>
+      <c r="AU79" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV79" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW79" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX79" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -1255,7 +1255,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -16375,10 +16375,8 @@
           <t>Structen Construction Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="O77" s="3" t="inlineStr">
-        <is>
-          <t>9803810701</t>
-        </is>
+      <c r="O77" s="3" t="n">
+        <v>9803810701</v>
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
@@ -16468,10 +16466,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN77" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN77" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO77" s="3" t="inlineStr">
         <is>
@@ -16482,7 +16478,7 @@
       <c r="AQ77" s="3" t="inlineStr"/>
       <c r="AR77" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS77" s="3" t="inlineStr">
@@ -16583,10 +16579,8 @@
           <t>Pramil Luitel</t>
         </is>
       </c>
-      <c r="O78" s="3" t="inlineStr">
-        <is>
-          <t>9841082626</t>
-        </is>
+      <c r="O78" s="3" t="n">
+        <v>9841082626</v>
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
@@ -16621,10 +16615,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y78" s="3" t="inlineStr">
-        <is>
-          <t>27.68994</t>
-        </is>
+      <c r="Y78" s="3" t="n">
+        <v>27.68994</v>
       </c>
       <c r="Z78" s="3" t="inlineStr">
         <is>
@@ -16680,25 +16672,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN78" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN78" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO78" s="3" t="inlineStr">
         <is>
           <t>3,9</t>
         </is>
       </c>
-      <c r="AP78" s="3" t="inlineStr">
-        <is>
-          <t>85.26628</t>
-        </is>
+      <c r="AP78" s="3" t="n">
+        <v>85.26627999999999</v>
       </c>
       <c r="AQ78" s="3" t="inlineStr"/>
       <c r="AR78" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS78" s="3" t="inlineStr">
@@ -16799,10 +16787,8 @@
           <t>Bedhari Chaulagain</t>
         </is>
       </c>
-      <c r="O79" s="3" t="inlineStr">
-        <is>
-          <t>9841121967</t>
-        </is>
+      <c r="O79" s="3" t="n">
+        <v>9841121967</v>
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
@@ -16837,10 +16823,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y79" s="3" t="inlineStr">
-        <is>
-          <t>27.71799</t>
-        </is>
+      <c r="Y79" s="3" t="n">
+        <v>27.71799</v>
       </c>
       <c r="Z79" s="3" t="inlineStr">
         <is>
@@ -16896,25 +16880,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN79" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN79" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO79" s="3" t="inlineStr">
         <is>
           <t>L2-8</t>
         </is>
       </c>
-      <c r="AP79" s="3" t="inlineStr">
-        <is>
-          <t>85.35404</t>
-        </is>
+      <c r="AP79" s="3" t="n">
+        <v>85.35404</v>
       </c>
       <c r="AQ79" s="3" t="inlineStr"/>
       <c r="AR79" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS79" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>93.8%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.6%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.6%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.4%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -893,26 +893,26 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>2</v>
@@ -921,26 +921,26 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>2</v>
@@ -977,11 +977,11 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>General Query &amp; Feedback</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -1005,11 +1005,11 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1071,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -1089,7 +1089,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -1117,7 +1117,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -1145,7 +1145,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -1164,38 +1164,66 @@
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B15" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G14" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>62</v>
+      <c r="G15" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1209,7 +1237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX79"/>
+  <dimension ref="A1:AX80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1255,7 +1283,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -16928,6 +16956,214 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 4:44 PM</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr"/>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347120</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>Manita Tamang</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
+          <t>Manita Tamang</t>
+        </is>
+      </c>
+      <c r="O80" s="3" t="inlineStr">
+        <is>
+          <t>9819840833</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q80" s="3" t="inlineStr"/>
+      <c r="R80" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 04:44:48 PM</t>
+        </is>
+      </c>
+      <c r="S80" s="3" t="inlineStr"/>
+      <c r="T80" s="3" t="inlineStr"/>
+      <c r="U80" s="3" t="inlineStr">
+        <is>
+          <t>9819840833</t>
+        </is>
+      </c>
+      <c r="V80" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:35:14 AM</t>
+        </is>
+      </c>
+      <c r="W80" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 04:44:48 PM</t>
+        </is>
+      </c>
+      <c r="X80" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y80" s="3" t="inlineStr"/>
+      <c r="Z80" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA80" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB80" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AC80" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD80" s="3" t="inlineStr"/>
+      <c r="AE80" s="3" t="inlineStr">
+        <is>
+          <t>Gurjudhara	Yatayat office	, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF80" s="3" t="inlineStr"/>
+      <c r="AG80" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH80" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI80" s="3" t="inlineStr">
+        <is>
+          <t>05:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ80" s="3" t="inlineStr"/>
+      <c r="AK80" s="3" t="inlineStr"/>
+      <c r="AL80" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM80" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN80" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO80" s="3" t="inlineStr">
+        <is>
+          <t>CDB301</t>
+        </is>
+      </c>
+      <c r="AP80" s="3" t="inlineStr"/>
+      <c r="AQ80" s="3" t="inlineStr"/>
+      <c r="AR80" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS80" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT80" s="3" t="inlineStr">
+        <is>
+          <t>5h 9m</t>
+        </is>
+      </c>
+      <c r="AU80" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV80" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW80" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX80" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.2%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.0%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>7</v>
@@ -859,7 +859,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -1208,7 +1208,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>11</v>
@@ -1223,7 +1223,7 @@
         <v>12</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX80"/>
+  <dimension ref="A1:AX81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17023,10 +17023,8 @@
           <t>Manita Tamang</t>
         </is>
       </c>
-      <c r="O80" s="3" t="inlineStr">
-        <is>
-          <t>9819840833</t>
-        </is>
+      <c r="O80" s="3" t="n">
+        <v>9819840833</v>
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
@@ -17094,10 +17092,8 @@
           <t>Router Upgrade Dual Band</t>
         </is>
       </c>
-      <c r="AH80" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH80" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI80" s="3" t="inlineStr">
         <is>
@@ -17116,10 +17112,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN80" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN80" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO80" s="3" t="inlineStr">
         <is>
@@ -17130,37 +17124,253 @@
       <c r="AQ80" s="3" t="inlineStr"/>
       <c r="AR80" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS80" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT80" s="3" t="inlineStr">
+        <is>
+          <t>5h 9m</t>
+        </is>
+      </c>
+      <c r="AU80" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV80" s="3" t="inlineStr">
+        <is>
           <t>Case : router upgrade  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS80" s="3" t="inlineStr">
+      <c r="AW80" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX80" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 4:59 PM</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr"/>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344657</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>Himal Ratna Tuladhar</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
+          <t>Himal Ratna Tuladhar</t>
+        </is>
+      </c>
+      <c r="O81" s="3" t="inlineStr">
+        <is>
+          <t>9841363726</t>
+        </is>
+      </c>
+      <c r="P81" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q81" s="3" t="inlineStr"/>
+      <c r="R81" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 04:59:46 PM</t>
+        </is>
+      </c>
+      <c r="S81" s="3" t="inlineStr"/>
+      <c r="T81" s="3" t="inlineStr"/>
+      <c r="U81" s="3" t="inlineStr">
+        <is>
+          <t>9841363726</t>
+        </is>
+      </c>
+      <c r="V81" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 11:07:59 AM</t>
+        </is>
+      </c>
+      <c r="W81" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 04:59:46 PM</t>
+        </is>
+      </c>
+      <c r="X81" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y81" s="3" t="inlineStr">
+        <is>
+          <t>27.70713</t>
+        </is>
+      </c>
+      <c r="Z81" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA81" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB81" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC81" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD81" s="3" t="inlineStr"/>
+      <c r="AE81" s="3" t="inlineStr">
+        <is>
+          <t>Century Commercial Bank Head Office Details from Google Maps P84F+V3W, Kathmandu 44600 +977 1-444506</t>
+        </is>
+      </c>
+      <c r="AF81" s="3" t="inlineStr">
+        <is>
+          <t>himalratna@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG81" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH81" s="3" t="inlineStr"/>
+      <c r="AI81" s="3" t="inlineStr">
+        <is>
+          <t>01:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ81" s="3" t="inlineStr"/>
+      <c r="AK81" s="3" t="inlineStr"/>
+      <c r="AL81" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM81" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN81" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO81" s="3" t="inlineStr">
+        <is>
+          <t>CDB543</t>
+        </is>
+      </c>
+      <c r="AP81" s="3" t="inlineStr">
+        <is>
+          <t>85.3221</t>
+        </is>
+      </c>
+      <c r="AQ81" s="3" t="inlineStr"/>
+      <c r="AR81" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS81" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT80" s="3" t="inlineStr">
-        <is>
-          <t>5h 9m</t>
-        </is>
-      </c>
-      <c r="AU80" s="3" t="inlineStr">
+      <c r="AT81" s="3" t="inlineStr">
+        <is>
+          <t>2d 5h 51m</t>
+        </is>
+      </c>
+      <c r="AU81" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV80" s="3" t="inlineStr">
-        <is>
-          <t>Case : router upgrade  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW80" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX80" s="3" t="inlineStr">
-        <is>
-          <t>Sunil Chaudhary</t>
+      <c r="AV81" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW81" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX81" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -1283,7 +1283,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -17225,10 +17225,8 @@
           <t>Himal Ratna Tuladhar</t>
         </is>
       </c>
-      <c r="O81" s="3" t="inlineStr">
-        <is>
-          <t>9841363726</t>
-        </is>
+      <c r="O81" s="3" t="n">
+        <v>9841363726</v>
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
@@ -17263,10 +17261,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y81" s="3" t="inlineStr">
-        <is>
-          <t>27.70713</t>
-        </is>
+      <c r="Y81" s="3" t="n">
+        <v>27.70713</v>
       </c>
       <c r="Z81" s="3" t="inlineStr">
         <is>
@@ -17322,25 +17318,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN81" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN81" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO81" s="3" t="inlineStr">
         <is>
           <t>CDB543</t>
         </is>
       </c>
-      <c r="AP81" s="3" t="inlineStr">
-        <is>
-          <t>85.3221</t>
-        </is>
+      <c r="AP81" s="3" t="n">
+        <v>85.32210000000001</v>
       </c>
       <c r="AQ81" s="3" t="inlineStr"/>
       <c r="AR81" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS81" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>89.5%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>25.3%</t>
         </is>
       </c>
     </row>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>53.0%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -884,35 +884,35 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>2</v>
@@ -921,26 +921,26 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>2</v>
@@ -949,11 +949,11 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Due to Optical Power flapping</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -977,7 +977,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>NETTV-No internet connection in STB</t>
+          <t>Due to Optical Power flapping</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -1005,11 +1005,11 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>General Query &amp; Feedback</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
@@ -1024,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>1</v>
@@ -1033,7 +1033,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Replace SKYCOM to NETTV</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Replace SKYCOM to NETTV</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1071,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -1089,7 +1089,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -1099,10 +1099,10 @@
         <v>0</v>
       </c>
       <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
@@ -1117,7 +1117,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>1</v>
@@ -1145,7 +1145,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -1173,7 +1173,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -1183,7 +1183,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
@@ -1192,38 +1192,66 @@
         <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B16" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C16" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D16" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E16" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F16" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>64</v>
+      <c r="G16" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX81"/>
+  <dimension ref="A1:AX84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1277,13 +1305,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -17366,6 +17394,630 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 5:30 PM</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr"/>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>iptv setbox issue</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>TKT1345845</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>Manju Kumari Sharma</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
+          <t>Manju Kumari Sharma</t>
+        </is>
+      </c>
+      <c r="O82" s="3" t="inlineStr">
+        <is>
+          <t>9841775966</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q82" s="3" t="inlineStr"/>
+      <c r="R82" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 11:56:55 AM</t>
+        </is>
+      </c>
+      <c r="S82" s="3" t="inlineStr"/>
+      <c r="T82" s="3" t="inlineStr"/>
+      <c r="U82" s="3" t="inlineStr">
+        <is>
+          <t>9841775966</t>
+        </is>
+      </c>
+      <c r="V82" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 11:08:15 AM</t>
+        </is>
+      </c>
+      <c r="W82" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 05:30:22 PM</t>
+        </is>
+      </c>
+      <c r="X82" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y82" s="3" t="inlineStr">
+        <is>
+          <t>27.721333</t>
+        </is>
+      </c>
+      <c r="Z82" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA82" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB82" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC82" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD82" s="3" t="inlineStr"/>
+      <c r="AE82" s="3" t="inlineStr">
+        <is>
+          <t>Thulo Bharyang, Nagarjun ward no:3,near Mina Dairy, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF82" s="3" t="inlineStr"/>
+      <c r="AG82" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH82" s="3" t="inlineStr"/>
+      <c r="AI82" s="3" t="inlineStr"/>
+      <c r="AJ82" s="3" t="inlineStr"/>
+      <c r="AK82" s="3" t="inlineStr"/>
+      <c r="AL82" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM82" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN82" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO82" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP82" s="3" t="inlineStr">
+        <is>
+          <t>85.281632</t>
+        </is>
+      </c>
+      <c r="AQ82" s="3" t="inlineStr"/>
+      <c r="AR82" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS82" s="3" t="inlineStr">
+        <is>
+          <t>1d 5h 33m</t>
+        </is>
+      </c>
+      <c r="AT82" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 22m</t>
+        </is>
+      </c>
+      <c r="AU82" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV82" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv setbox issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW82" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX82" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 5:22 PM</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343590</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>Susmita sherstha</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
+          <t>Susmita sherstha</t>
+        </is>
+      </c>
+      <c r="O83" s="3" t="inlineStr">
+        <is>
+          <t>9803435164</t>
+        </is>
+      </c>
+      <c r="P83" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q83" s="3" t="inlineStr"/>
+      <c r="R83" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 03:26:50 PM</t>
+        </is>
+      </c>
+      <c r="S83" s="3" t="inlineStr"/>
+      <c r="T83" s="3" t="inlineStr"/>
+      <c r="U83" s="3" t="inlineStr">
+        <is>
+          <t>KLK9803435164</t>
+        </is>
+      </c>
+      <c r="V83" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 11:34:40 AM</t>
+        </is>
+      </c>
+      <c r="W83" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 05:22:30 PM</t>
+        </is>
+      </c>
+      <c r="X83" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y83" s="3" t="inlineStr"/>
+      <c r="Z83" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA83" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB83" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC83" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD83" s="3" t="inlineStr"/>
+      <c r="AE83" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu chandragiri 12 , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF83" s="3" t="inlineStr">
+        <is>
+          <t>unknown@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG83" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH83" s="3" t="inlineStr"/>
+      <c r="AI83" s="3" t="inlineStr">
+        <is>
+          <t>11:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ83" s="3" t="inlineStr"/>
+      <c r="AK83" s="3" t="inlineStr"/>
+      <c r="AL83" s="3" t="inlineStr">
+        <is>
+          <t>Shanti Pokhrel</t>
+        </is>
+      </c>
+      <c r="AM83" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN83" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO83" s="3" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="AP83" s="3" t="inlineStr"/>
+      <c r="AQ83" s="3" t="inlineStr"/>
+      <c r="AR83" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS83" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 55m</t>
+        </is>
+      </c>
+      <c r="AT83" s="3" t="inlineStr">
+        <is>
+          <t>3d 5h 47m</t>
+        </is>
+      </c>
+      <c r="AU83" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV83" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW83" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX83" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 5:21 PM</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr"/>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>TKT1343590</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>Susmita sherstha</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
+          <t>Susmita sherstha</t>
+        </is>
+      </c>
+      <c r="O84" s="3" t="inlineStr">
+        <is>
+          <t>9803435164</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q84" s="3" t="inlineStr"/>
+      <c r="R84" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 03:26:50 PM</t>
+        </is>
+      </c>
+      <c r="S84" s="3" t="inlineStr"/>
+      <c r="T84" s="3" t="inlineStr"/>
+      <c r="U84" s="3" t="inlineStr">
+        <is>
+          <t>KLK9803435164</t>
+        </is>
+      </c>
+      <c r="V84" s="3" t="inlineStr">
+        <is>
+          <t>23 Sep 2026 11:34:40 AM</t>
+        </is>
+      </c>
+      <c r="W84" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 05:22:30 PM</t>
+        </is>
+      </c>
+      <c r="X84" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y84" s="3" t="inlineStr"/>
+      <c r="Z84" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA84" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB84" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC84" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD84" s="3" t="inlineStr"/>
+      <c r="AE84" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu chandragiri 12 , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF84" s="3" t="inlineStr">
+        <is>
+          <t>unknown@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG84" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH84" s="3" t="inlineStr"/>
+      <c r="AI84" s="3" t="inlineStr">
+        <is>
+          <t>11:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ84" s="3" t="inlineStr"/>
+      <c r="AK84" s="3" t="inlineStr"/>
+      <c r="AL84" s="3" t="inlineStr">
+        <is>
+          <t>Shanti Pokhrel</t>
+        </is>
+      </c>
+      <c r="AM84" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN84" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO84" s="3" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="AP84" s="3" t="inlineStr"/>
+      <c r="AQ84" s="3" t="inlineStr"/>
+      <c r="AR84" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS84" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 55m</t>
+        </is>
+      </c>
+      <c r="AT84" s="3" t="inlineStr">
+        <is>
+          <t>3d 5h 47m</t>
+        </is>
+      </c>
+      <c r="AU84" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV84" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW84" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX84" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_26_Sep_2026.xlsx
@@ -1311,7 +1311,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="45" customWidth="1" min="47" max="47"/>
@@ -17461,10 +17461,8 @@
           <t>Manju Kumari Sharma</t>
         </is>
       </c>
-      <c r="O82" s="3" t="inlineStr">
-        <is>
-          <t>9841775966</t>
-        </is>
+      <c r="O82" s="3" t="n">
+        <v>9841775966</v>
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
@@ -17499,10 +17497,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y82" s="3" t="inlineStr">
-        <is>
-          <t>27.721333</t>
-        </is>
+      <c r="Y82" s="3" t="n">
+        <v>27.721333</v>
       </c>
       <c r="Z82" s="3" t="inlineStr">
         <is>
@@ -17550,25 +17546,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN82" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN82" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO82" s="3" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="AP82" s="3" t="inlineStr">
-        <is>
-          <t>85.281632</t>
-        </is>
+      <c r="AP82" s="3" t="n">
+        <v>85.281632</v>
       </c>
       <c r="AQ82" s="3" t="inlineStr"/>
       <c r="AR82" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv setbox issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS82" s="3" t="inlineStr">
@@ -17659,20 +17651,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M83" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M83" s="3" t="inlineStr"/>
       <c r="N83" s="3" t="inlineStr">
         <is>
           <t>Susmita sherstha</t>
         </is>
       </c>
-      <c r="O83" s="3" t="inlineStr">
-        <is>
-          <t>9803435164</t>
-        </is>
+      <c r="O83" s="3" t="n">
+        <v>9803435164</v>
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
@@ -17762,10 +17748,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN83" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN83" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO83" s="3" t="inlineStr">
         <is>
@@ -17776,7 +17760,7 @@
       <c r="AQ83" s="3" t="inlineStr"/>
       <c r="AR83" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS83" s="3" t="inlineStr">
@@ -17867,20 +17851,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M84" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M84" s="3" t="inlineStr"/>
       <c r="N84" s="3" t="inlineStr">
         <is>
           <t>Susmita sherstha</t>
         </is>
       </c>
-      <c r="O84" s="3" t="inlineStr">
-        <is>
-          <t>9803435164</t>
-        </is>
+      <c r="O84" s="3" t="n">
+        <v>9803435164</v>
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
@@ -17970,10 +17948,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN84" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN84" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO84" s="3" t="inlineStr">
         <is>
@@ -17984,7 +17960,7 @@
       <c r="AQ84" s="3" t="inlineStr"/>
       <c r="AR84" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV Issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS84" s="3" t="inlineStr">
